--- a/etf_holdings.xlsx
+++ b/etf_holdings.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="00981A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="00984A" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="00993A" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="00986A" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="00987A" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="00994A" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ALL" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00981A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00984A" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00993A" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00986A" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00987A" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00994A" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALL" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,16 +23,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -51,21 +48,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,32 +423,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ETF代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>股數</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>權重(%)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
@@ -472,10 +460,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B2" t="n">
+        <v>2330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -500,10 +486,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B3" t="n">
+        <v>2383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -528,10 +512,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B4" t="n">
+        <v>2308</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -556,10 +538,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B5" t="n">
+        <v>2368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -584,10 +564,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B6" t="n">
+        <v>3017</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -612,10 +590,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B7" t="n">
+        <v>6223</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -640,10 +616,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3653</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -668,10 +642,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B9" t="n">
+        <v>2345</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -696,10 +668,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3665</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -724,10 +694,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3037</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -752,10 +720,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
+      <c r="B12" t="n">
+        <v>2327</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -780,10 +746,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
+      <c r="B13" t="n">
+        <v>5274</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -808,10 +772,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
+      <c r="B14" t="n">
+        <v>8046</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -836,10 +798,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
+      <c r="B15" t="n">
+        <v>6510</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -864,10 +824,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3661</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -892,10 +850,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2449</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -920,10 +876,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>8210</t>
-        </is>
+      <c r="B18" t="n">
+        <v>8210</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -948,10 +902,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
+      <c r="B19" t="n">
+        <v>6515</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -976,10 +928,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
+      <c r="B20" t="n">
+        <v>3711</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1004,10 +954,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1303</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1032,10 +980,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B22" t="n">
+        <v>6805</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1060,10 +1006,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>6139</t>
-        </is>
+      <c r="B23" t="n">
+        <v>6139</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1088,10 +1032,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2454</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1116,10 +1058,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>6488</t>
-        </is>
+      <c r="B25" t="n">
+        <v>6488</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1144,10 +1084,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B26" t="n">
+        <v>6274</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1172,10 +1110,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
+      <c r="B27" t="n">
+        <v>6669</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1200,10 +1136,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
+      <c r="B28" t="n">
+        <v>2404</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1228,10 +1162,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
+      <c r="B29" t="n">
+        <v>8358</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1256,10 +1188,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3211</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3211</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1284,10 +1214,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3189</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1312,10 +1240,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>4979</t>
-        </is>
+      <c r="B32" t="n">
+        <v>4979</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1340,10 +1266,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
+      <c r="B33" t="n">
+        <v>1326</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1368,10 +1292,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
+      <c r="B34" t="n">
+        <v>1802</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1396,10 +1318,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
+      <c r="B35" t="n">
+        <v>2408</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1424,10 +1344,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>6191</t>
-        </is>
+      <c r="B36" t="n">
+        <v>6191</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1452,10 +1370,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>3376</t>
-        </is>
+      <c r="B37" t="n">
+        <v>3376</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1480,10 +1396,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
+      <c r="B38" t="n">
+        <v>8996</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1508,10 +1422,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>3264</t>
-        </is>
+      <c r="B39" t="n">
+        <v>3264</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1536,10 +1448,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>3533</t>
-        </is>
+      <c r="B40" t="n">
+        <v>3533</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1564,10 +1474,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>3324</t>
-        </is>
+      <c r="B41" t="n">
+        <v>3324</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1592,10 +1500,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
+      <c r="B42" t="n">
+        <v>1319</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1620,10 +1526,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
+      <c r="B43" t="n">
+        <v>2002</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1648,10 +1552,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>3217</t>
-        </is>
+      <c r="B44" t="n">
+        <v>3217</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1676,10 +1578,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
+      <c r="B45" t="n">
+        <v>3008</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1704,10 +1604,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
+      <c r="B46" t="n">
+        <v>2059</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1732,10 +1630,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2357</t>
-        </is>
+      <c r="B47" t="n">
+        <v>2357</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1760,10 +1656,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>1815</t>
-        </is>
+      <c r="B48" t="n">
+        <v>1815</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1788,10 +1682,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2439</t>
-        </is>
+      <c r="B49" t="n">
+        <v>2439</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1816,10 +1708,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
+      <c r="B50" t="n">
+        <v>8299</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1844,10 +1734,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>3045</t>
-        </is>
+      <c r="B51" t="n">
+        <v>3045</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1872,10 +1760,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>5536</t>
-        </is>
+      <c r="B52" t="n">
+        <v>5536</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1900,10 +1786,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
+      <c r="B53" t="n">
+        <v>2313</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1928,10 +1812,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>3583</t>
-        </is>
+      <c r="B54" t="n">
+        <v>3583</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1965,32 +1847,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ETF代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>股數</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>權重(%)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
@@ -2002,10 +1884,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B2" t="n">
+        <v>2330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2034,10 +1914,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2382</t>
-        </is>
+      <c r="B3" t="n">
+        <v>2382</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2066,10 +1944,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2881</t>
-        </is>
+      <c r="B4" t="n">
+        <v>2881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2098,10 +1974,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>3045</t>
-        </is>
+      <c r="B5" t="n">
+        <v>3045</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2130,10 +2004,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
+      <c r="B6" t="n">
+        <v>2882</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2162,10 +2034,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
+      <c r="B7" t="n">
+        <v>2891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2194,10 +2064,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2303</t>
-        </is>
+      <c r="B8" t="n">
+        <v>2303</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2226,10 +2094,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
+      <c r="B9" t="n">
+        <v>2885</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2258,10 +2124,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
+      <c r="B10" t="n">
+        <v>2880</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2290,10 +2154,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
+      <c r="B11" t="n">
+        <v>2887</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2322,10 +2184,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3036</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3036</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2354,10 +2214,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
+      <c r="B13" t="n">
+        <v>2883</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2386,10 +2244,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>4904</t>
-        </is>
+      <c r="B14" t="n">
+        <v>4904</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2418,10 +2274,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1102</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2450,10 +2304,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2379</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2379</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2482,10 +2334,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B17" t="n">
+        <v>3037</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2514,10 +2364,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
+      <c r="B18" t="n">
+        <v>5274</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2546,10 +2394,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2603</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2603</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2578,10 +2424,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>5289</t>
-        </is>
+      <c r="B20" t="n">
+        <v>5289</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2610,10 +2454,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1402</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1402</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2642,10 +2484,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2324</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2324</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2674,10 +2514,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3264</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3264</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2706,10 +2544,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
+      <c r="B24" t="n">
+        <v>8299</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2738,10 +2574,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2357</t>
-        </is>
+      <c r="B25" t="n">
+        <v>2357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2770,10 +2604,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B26" t="n">
+        <v>2383</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -2802,10 +2634,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3711</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -2834,10 +2664,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B28" t="n">
+        <v>2308</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -2866,10 +2694,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
+      <c r="B29" t="n">
+        <v>6515</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2898,10 +2724,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1560</t>
-        </is>
+      <c r="B30" t="n">
+        <v>1560</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2930,10 +2754,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2912</t>
-        </is>
+      <c r="B31" t="n">
+        <v>2912</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -2962,10 +2784,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>9904</t>
-        </is>
+      <c r="B32" t="n">
+        <v>9904</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2994,10 +2814,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3260</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3260</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3026,10 +2844,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="B34" t="n">
+        <v>2360</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3058,10 +2874,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
+      <c r="B35" t="n">
+        <v>2449</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -3090,10 +2904,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>8112</t>
-        </is>
+      <c r="B36" t="n">
+        <v>8112</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -3122,10 +2934,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>4938</t>
-        </is>
+      <c r="B37" t="n">
+        <v>4938</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -3154,10 +2964,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
+      <c r="B38" t="n">
+        <v>2618</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -3186,10 +2994,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
+      <c r="B39" t="n">
+        <v>1303</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -3218,10 +3024,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>6005</t>
-        </is>
+      <c r="B40" t="n">
+        <v>6005</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -3250,10 +3054,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>6446</t>
-        </is>
+      <c r="B41" t="n">
+        <v>6446</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -3282,10 +3084,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>3491</t>
-        </is>
+      <c r="B42" t="n">
+        <v>3491</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -3314,10 +3114,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
+      <c r="B43" t="n">
+        <v>2376</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -3346,10 +3144,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>6691</t>
-        </is>
+      <c r="B44" t="n">
+        <v>6691</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -3378,10 +3174,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>3105</t>
-        </is>
+      <c r="B45" t="n">
+        <v>3105</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -3410,10 +3204,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>8021</t>
-        </is>
+      <c r="B46" t="n">
+        <v>8021</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -3442,10 +3234,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>3702</t>
-        </is>
+      <c r="B47" t="n">
+        <v>3702</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -3474,10 +3264,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>6239</t>
-        </is>
+      <c r="B48" t="n">
+        <v>6239</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -3506,10 +3294,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>1785</t>
-        </is>
+      <c r="B49" t="n">
+        <v>1785</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -3538,10 +3324,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2441</t>
-        </is>
+      <c r="B50" t="n">
+        <v>2441</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -3570,10 +3354,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2610</t>
-        </is>
+      <c r="B51" t="n">
+        <v>2610</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -3602,10 +3384,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>3006</t>
-        </is>
+      <c r="B52" t="n">
+        <v>3006</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -3634,10 +3414,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B53" t="n">
+        <v>6223</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -3666,10 +3444,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>1605</t>
-        </is>
+      <c r="B54" t="n">
+        <v>1605</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -3698,10 +3474,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
+      <c r="B55" t="n">
+        <v>2313</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -3730,10 +3504,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2467</t>
-        </is>
+      <c r="B56" t="n">
+        <v>2467</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -3762,10 +3534,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2486</t>
-        </is>
+      <c r="B57" t="n">
+        <v>2486</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -3794,10 +3564,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
+      <c r="B58" t="n">
+        <v>3189</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3826,10 +3594,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
+      <c r="B59" t="n">
+        <v>6510</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -3858,10 +3624,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2474</t>
-        </is>
+      <c r="B60" t="n">
+        <v>2474</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3890,10 +3654,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>3081</t>
-        </is>
+      <c r="B61" t="n">
+        <v>3081</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3922,10 +3684,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
+      <c r="B62" t="n">
+        <v>3481</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3954,10 +3714,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
+      <c r="B63" t="n">
+        <v>2344</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3986,10 +3744,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2385</t>
-        </is>
+      <c r="B64" t="n">
+        <v>2385</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -4018,10 +3774,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
+      <c r="B65" t="n">
+        <v>2890</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -4050,10 +3804,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>1815</t>
-        </is>
+      <c r="B66" t="n">
+        <v>1815</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -4082,10 +3834,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>6282</t>
-        </is>
+      <c r="B67" t="n">
+        <v>6282</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -4114,10 +3864,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>6290</t>
-        </is>
+      <c r="B68" t="n">
+        <v>6290</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -4146,10 +3894,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
+      <c r="B69" t="n">
+        <v>6770</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -4178,10 +3924,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>6903</t>
-        </is>
+      <c r="B70" t="n">
+        <v>6903</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -4210,10 +3954,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
+      <c r="B71" t="n">
+        <v>8046</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -4242,10 +3984,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2492</t>
-        </is>
+      <c r="B72" t="n">
+        <v>2492</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -4274,10 +4014,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>5234</t>
-        </is>
+      <c r="B73" t="n">
+        <v>5234</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -4306,10 +4044,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>6548</t>
-        </is>
+      <c r="B74" t="n">
+        <v>6548</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -4338,10 +4074,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>6257</t>
-        </is>
+      <c r="B75" t="n">
+        <v>6257</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -4370,10 +4104,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>7795</t>
-        </is>
+      <c r="B76" t="n">
+        <v>7795</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -4402,10 +4134,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
+      <c r="B77" t="n">
+        <v>1326</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -4434,10 +4164,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
+      <c r="B78" t="n">
+        <v>1519</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -4466,10 +4194,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B79" t="n">
+        <v>2345</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -4498,10 +4224,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>3374</t>
-        </is>
+      <c r="B80" t="n">
+        <v>3374</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4530,10 +4254,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
+      <c r="B81" t="n">
+        <v>7769</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4562,10 +4284,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B82" t="n">
+        <v>2368</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -4594,10 +4314,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>9910</t>
-        </is>
+      <c r="B83" t="n">
+        <v>9910</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -4626,10 +4344,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>6442</t>
-        </is>
+      <c r="B84" t="n">
+        <v>6442</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -4658,10 +4374,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2851</t>
-        </is>
+      <c r="B85" t="n">
+        <v>2851</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4690,10 +4404,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
+      <c r="B86" t="n">
+        <v>2006</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4722,10 +4434,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>3010</t>
-        </is>
+      <c r="B87" t="n">
+        <v>3010</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -4754,10 +4464,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>1227</t>
-        </is>
+      <c r="B88" t="n">
+        <v>1227</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4786,10 +4494,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2501</t>
-        </is>
+      <c r="B89" t="n">
+        <v>2501</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4818,10 +4524,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>2850</t>
-        </is>
+      <c r="B90" t="n">
+        <v>2850</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4850,10 +4554,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>2897</t>
-        </is>
+      <c r="B91" t="n">
+        <v>2897</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -4882,10 +4584,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>2903</t>
-        </is>
+      <c r="B92" t="n">
+        <v>2903</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -4914,10 +4614,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>8070</t>
-        </is>
+      <c r="B93" t="n">
+        <v>8070</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -4946,10 +4644,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2637</t>
-        </is>
+      <c r="B94" t="n">
+        <v>2637</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -4978,10 +4674,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2820</t>
-        </is>
+      <c r="B95" t="n">
+        <v>2820</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -5010,10 +4704,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2855</t>
-        </is>
+      <c r="B96" t="n">
+        <v>2855</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -5042,10 +4734,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>3227</t>
-        </is>
+      <c r="B97" t="n">
+        <v>3227</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -5074,10 +4764,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>9907</t>
-        </is>
+      <c r="B98" t="n">
+        <v>9907</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -5106,10 +4794,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>1434</t>
-        </is>
+      <c r="B99" t="n">
+        <v>1434</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -5138,10 +4824,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
+      <c r="B100" t="n">
+        <v>3443</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -5170,10 +4854,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
+      <c r="B101" t="n">
+        <v>8358</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -5202,10 +4884,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B102" t="n">
+        <v>3017</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -5234,10 +4914,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
+      <c r="B103" t="n">
+        <v>2327</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -5266,10 +4944,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>6023</t>
-        </is>
+      <c r="B104" t="n">
+        <v>6023</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -5298,10 +4974,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B105" t="n">
+        <v>6274</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -5330,10 +5004,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>3005</t>
-        </is>
+      <c r="B106" t="n">
+        <v>3005</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -5362,10 +5034,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2458</t>
-        </is>
+      <c r="B107" t="n">
+        <v>2458</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -5394,10 +5064,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
+      <c r="B108" t="n">
+        <v>2353</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -5426,10 +5094,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>6121</t>
-        </is>
+      <c r="B109" t="n">
+        <v>6121</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -5458,10 +5124,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>9917</t>
-        </is>
+      <c r="B110" t="n">
+        <v>9917</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -5490,10 +5154,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>2206</t>
-        </is>
+      <c r="B111" t="n">
+        <v>2206</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -5522,10 +5184,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>2352</t>
-        </is>
+      <c r="B112" t="n">
+        <v>2352</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -5554,10 +5214,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>2377</t>
-        </is>
+      <c r="B113" t="n">
+        <v>2377</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -5586,10 +5244,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>4766</t>
-        </is>
+      <c r="B114" t="n">
+        <v>4766</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -5618,10 +5274,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>6414</t>
-        </is>
+      <c r="B115" t="n">
+        <v>6414</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -5650,10 +5304,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>8415</t>
-        </is>
+      <c r="B116" t="n">
+        <v>8415</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -5682,10 +5334,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>9939</t>
-        </is>
+      <c r="B117" t="n">
+        <v>9939</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -5714,10 +5364,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>1795</t>
-        </is>
+      <c r="B118" t="n">
+        <v>1795</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -5746,10 +5394,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>6176</t>
-        </is>
+      <c r="B119" t="n">
+        <v>6176</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -5778,10 +5424,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B120" t="n">
+        <v>3653</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -5810,10 +5454,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B121" t="n">
+        <v>6805</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -5842,10 +5484,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
+      <c r="B122" t="n">
+        <v>2301</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -5883,32 +5523,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ETF代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>股數</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>權重(%)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
@@ -5920,10 +5560,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>3036</t>
-        </is>
+      <c r="B2" t="n">
+        <v>3036</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5952,10 +5590,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
+      <c r="B3" t="n">
+        <v>2412</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -5984,10 +5620,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B4" t="n">
+        <v>2330</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -6016,10 +5650,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2303</t>
-        </is>
+      <c r="B5" t="n">
+        <v>2303</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -6048,10 +5680,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
+      <c r="B6" t="n">
+        <v>2454</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -6080,10 +5710,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3044</t>
-        </is>
+      <c r="B7" t="n">
+        <v>3044</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -6112,10 +5740,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
+      <c r="B8" t="n">
+        <v>2344</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -6144,10 +5770,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1590</t>
-        </is>
+      <c r="B9" t="n">
+        <v>1590</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -6176,10 +5800,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
+      <c r="B10" t="n">
+        <v>2327</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -6208,10 +5830,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3037</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -6240,10 +5860,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="B12" t="n">
+        <v>2360</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -6272,10 +5890,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B13" t="n">
+        <v>2383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -6304,10 +5920,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3167</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3167</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -6336,10 +5950,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
+      <c r="B15" t="n">
+        <v>8996</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -6368,10 +5980,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3105</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3105</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -6400,10 +6010,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
+      <c r="B17" t="n">
+        <v>6515</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -6432,10 +6040,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2313</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -6464,10 +6070,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2368</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -6496,10 +6100,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2337</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -6528,10 +6130,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
+      <c r="B21" t="n">
+        <v>6770</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -6560,10 +6160,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3533</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3533</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -6592,10 +6190,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2308</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -6624,10 +6220,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3017</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -6656,10 +6250,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3481</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -6688,10 +6280,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>6285</t>
-        </is>
+      <c r="B26" t="n">
+        <v>6285</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -6720,10 +6310,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
+      <c r="B27" t="n">
+        <v>1303</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -6752,10 +6340,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3653</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -6784,10 +6370,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B29" t="n">
+        <v>6223</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -6816,10 +6400,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B30" t="n">
+        <v>2345</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -6848,10 +6430,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
+      <c r="B31" t="n">
+        <v>2883</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -6880,10 +6460,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1815</t>
-        </is>
+      <c r="B32" t="n">
+        <v>1815</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -6912,10 +6490,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3324</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3324</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -6944,10 +6520,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3715</t>
-        </is>
+      <c r="B34" t="n">
+        <v>3715</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -6976,10 +6550,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>3264</t>
-        </is>
+      <c r="B35" t="n">
+        <v>3264</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -7008,10 +6580,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>3491</t>
-        </is>
+      <c r="B36" t="n">
+        <v>3491</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -7040,10 +6610,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B37" t="n">
+        <v>6805</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -7072,10 +6640,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
+      <c r="B38" t="n">
+        <v>8358</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -7104,10 +6670,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
+      <c r="B39" t="n">
+        <v>8299</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -7136,10 +6700,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>6290</t>
-        </is>
+      <c r="B40" t="n">
+        <v>6290</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -7168,10 +6730,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
+      <c r="B41" t="n">
+        <v>2882</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -7200,10 +6760,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B42" t="n">
+        <v>6274</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -7232,10 +6790,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>1560</t>
-        </is>
+      <c r="B43" t="n">
+        <v>1560</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -7264,10 +6820,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>6446</t>
-        </is>
+      <c r="B44" t="n">
+        <v>6446</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -7296,10 +6850,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>4722</t>
-        </is>
+      <c r="B45" t="n">
+        <v>4722</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -7328,10 +6880,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
+      <c r="B46" t="n">
+        <v>2449</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -7360,10 +6910,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>8021</t>
-        </is>
+      <c r="B47" t="n">
+        <v>8021</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -7392,10 +6940,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
+      <c r="B48" t="n">
+        <v>1519</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7424,10 +6970,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
+      <c r="B49" t="n">
+        <v>5274</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7456,10 +7000,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>6442</t>
-        </is>
+      <c r="B50" t="n">
+        <v>6442</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7488,10 +7030,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>7751</t>
-        </is>
+      <c r="B51" t="n">
+        <v>7751</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7529,32 +7069,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ETF代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>股數</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>權重(%)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
@@ -8631,32 +8171,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ETF代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>股數</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>權重(%)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
@@ -8668,10 +8208,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B2" t="n">
+        <v>2330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8700,10 +8238,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B3" t="n">
+        <v>3017</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -8732,10 +8268,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
+      <c r="B4" t="n">
+        <v>8299</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -8764,10 +8298,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
+      <c r="B5" t="n">
+        <v>7769</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -8796,10 +8328,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B6" t="n">
+        <v>6223</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -8828,10 +8358,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B7" t="n">
+        <v>3653</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -8860,10 +8388,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B8" t="n">
+        <v>2308</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -8892,10 +8418,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B9" t="n">
+        <v>2345</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -8924,10 +8448,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
+      <c r="B10" t="n">
+        <v>2344</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -8956,10 +8478,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3363</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3363</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -8988,10 +8508,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B12" t="n">
+        <v>2368</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -9020,10 +8538,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B13" t="n">
+        <v>6274</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -9052,10 +8568,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
+      <c r="B14" t="n">
+        <v>8358</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -9084,10 +8598,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3665</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -9116,10 +8628,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2383</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -9148,10 +8658,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B17" t="n">
+        <v>6805</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -9180,10 +8688,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B18" t="n">
+        <v>3037</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -9212,10 +8718,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
+      <c r="B19" t="n">
+        <v>3443</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -9244,10 +8748,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>6683</t>
-        </is>
+      <c r="B20" t="n">
+        <v>6683</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -9276,10 +8778,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2337</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -9308,10 +8808,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
+      <c r="B22" t="n">
+        <v>6510</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -9340,10 +8838,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2360</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -9372,10 +8868,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2455</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2455</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -9404,10 +8898,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
+      <c r="B25" t="n">
+        <v>6770</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -9436,10 +8928,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>5234</t>
-        </is>
+      <c r="B26" t="n">
+        <v>5234</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -9477,32 +8967,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ETF代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>股數</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>權重(%)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
@@ -9514,10 +9004,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B2" t="n">
+        <v>2308</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9529,10 +9017,8 @@
           <t>31,500</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4.34</t>
-        </is>
+      <c r="E2" t="n">
+        <v>4.34</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9546,10 +9032,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
+      <c r="B3" t="n">
+        <v>2313</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -9561,10 +9045,8 @@
           <t>88,000</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
+      <c r="E3" t="n">
+        <v>1.99</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -9578,10 +9060,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B4" t="n">
+        <v>2330</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -9593,10 +9073,8 @@
           <t>106,999</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>19.16</t>
-        </is>
+      <c r="E4" t="n">
+        <v>19.16</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -9610,10 +9088,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B5" t="n">
+        <v>2345</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -9625,10 +9101,8 @@
           <t>32,000</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>4.46</t>
-        </is>
+      <c r="E5" t="n">
+        <v>4.46</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -9642,10 +9116,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="B6" t="n">
+        <v>2360</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -9657,10 +9129,8 @@
           <t>33,000</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>4.64</t>
-        </is>
+      <c r="E6" t="n">
+        <v>4.64</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -9674,10 +9144,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B7" t="n">
+        <v>2368</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -9689,10 +9157,8 @@
           <t>46,000</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>4.04</t>
-        </is>
+      <c r="E7" t="n">
+        <v>4.04</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -9706,10 +9172,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B8" t="n">
+        <v>2383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -9721,10 +9185,8 @@
           <t>22,000</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>5.68</t>
-        </is>
+      <c r="E8" t="n">
+        <v>5.68</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -9738,10 +9200,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
+      <c r="B9" t="n">
+        <v>2408</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -9753,10 +9213,8 @@
           <t>62,000</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
+      <c r="E9" t="n">
+        <v>1.61</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -9770,10 +9228,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
+      <c r="B10" t="n">
+        <v>2449</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -9785,10 +9241,8 @@
           <t>87,000</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="E10" t="n">
+        <v>2.45</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -9802,10 +9256,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
+      <c r="B11" t="n">
+        <v>2454</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -9817,10 +9269,8 @@
           <t>1,000</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
+      <c r="E11" t="n">
+        <v>0.17</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -9834,10 +9284,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2467</t>
-        </is>
+      <c r="B12" t="n">
+        <v>2467</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -9849,10 +9297,8 @@
           <t>20,000</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
+      <c r="E12" t="n">
+        <v>0.72</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -9866,10 +9312,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3017</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -9881,10 +9325,8 @@
           <t>30,500</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>5.56</t>
-        </is>
+      <c r="E13" t="n">
+        <v>5.56</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -9898,10 +9340,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3037</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -9913,10 +9353,8 @@
           <t>131,001</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>6.81</t>
-        </is>
+      <c r="E14" t="n">
+        <v>6.81</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -9930,10 +9368,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3260</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3260</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -9945,10 +9381,8 @@
           <t>44,000</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
+      <c r="E15" t="n">
+        <v>1.83</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -9962,10 +9396,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3324</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3324</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -9977,10 +9409,8 @@
           <t>4,000</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
+      <c r="E16" t="n">
+        <v>0.4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -9994,10 +9424,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B17" t="n">
+        <v>3653</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -10009,10 +9437,8 @@
           <t>9,000</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>3.21</t>
-        </is>
+      <c r="E17" t="n">
+        <v>3.21</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -10026,10 +9452,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
+      <c r="B18" t="n">
+        <v>3665</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -10041,10 +9465,8 @@
           <t>13,000</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2.16</t>
-        </is>
+      <c r="E18" t="n">
+        <v>2.16</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -10058,10 +9480,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
+      <c r="B19" t="n">
+        <v>3711</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -10073,10 +9493,8 @@
           <t>54,000</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
+      <c r="E19" t="n">
+        <v>1.77</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -10090,10 +9508,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>4904</t>
-        </is>
+      <c r="B20" t="n">
+        <v>4904</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -10105,10 +9521,8 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="E20" t="n">
+        <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -10122,10 +9536,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
+      <c r="B21" t="n">
+        <v>5274</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -10137,10 +9549,8 @@
           <t>3,600</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="E21" t="n">
+        <v>3.9</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -10154,10 +9564,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B22" t="n">
+        <v>6223</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -10169,10 +9577,8 @@
           <t>13,000</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>4.45</t>
-        </is>
+      <c r="E22" t="n">
+        <v>4.45</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -10186,10 +9592,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>6257</t>
-        </is>
+      <c r="B23" t="n">
+        <v>6257</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -10201,10 +9605,8 @@
           <t>45,000</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
+      <c r="E23" t="n">
+        <v>0.57</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -10218,10 +9620,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B24" t="n">
+        <v>6274</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -10233,10 +9633,8 @@
           <t>24,000</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
+      <c r="E24" t="n">
+        <v>1.16</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -10250,10 +9648,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>6442</t>
-        </is>
+      <c r="B25" t="n">
+        <v>6442</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -10265,10 +9661,8 @@
           <t>4,000</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
+      <c r="E25" t="n">
+        <v>0.65</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -10282,10 +9676,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
+      <c r="B26" t="n">
+        <v>6510</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -10297,10 +9689,8 @@
           <t>8,000</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2.89</t>
-        </is>
+      <c r="E26" t="n">
+        <v>2.89</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -10314,10 +9704,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
+      <c r="B27" t="n">
+        <v>6515</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -10329,10 +9717,8 @@
           <t>8,100</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>5.13</t>
-        </is>
+      <c r="E27" t="n">
+        <v>5.13</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -10346,10 +9732,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B28" t="n">
+        <v>6805</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -10361,10 +9745,8 @@
           <t>17,001</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2.84</t>
-        </is>
+      <c r="E28" t="n">
+        <v>2.84</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -10378,10 +9760,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
+      <c r="B29" t="n">
+        <v>7769</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -10393,10 +9773,8 @@
           <t>3,000</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
+      <c r="E29" t="n">
+        <v>1.21</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -10410,10 +9788,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
+      <c r="B30" t="n">
+        <v>8046</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -10425,10 +9801,8 @@
           <t>39,000</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
+      <c r="E30" t="n">
+        <v>2.03</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -10442,10 +9816,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
+      <c r="B31" t="n">
+        <v>8299</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -10457,10 +9829,8 @@
           <t>8,000</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
+      <c r="E31" t="n">
+        <v>1.49</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -10474,10 +9844,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
+      <c r="B32" t="n">
+        <v>8358</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -10489,10 +9857,8 @@
           <t>20,000</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
+      <c r="E32" t="n">
+        <v>0.5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -10506,10 +9872,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
+      <c r="B33" t="n">
+        <v>8996</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -10521,10 +9885,8 @@
           <t>10,000</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
+      <c r="E33" t="n">
+        <v>0.88</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -10547,32 +9909,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ETF代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>股票代號</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>股票名稱</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>股數</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>權重(%)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
@@ -10584,10 +9946,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B2" t="n">
+        <v>2330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10612,10 +9972,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B3" t="n">
+        <v>2383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -10640,10 +9998,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B4" t="n">
+        <v>2308</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -10668,10 +10024,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B5" t="n">
+        <v>2368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -10696,10 +10050,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B6" t="n">
+        <v>3017</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -10724,10 +10076,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B7" t="n">
+        <v>6223</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -10752,10 +10102,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3653</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -10780,10 +10128,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B9" t="n">
+        <v>2345</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -10808,10 +10154,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3665</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -10836,10 +10180,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3037</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -10864,10 +10206,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
+      <c r="B12" t="n">
+        <v>2327</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -10892,10 +10232,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
+      <c r="B13" t="n">
+        <v>5274</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -10920,10 +10258,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
+      <c r="B14" t="n">
+        <v>8046</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -10948,10 +10284,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
+      <c r="B15" t="n">
+        <v>6510</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -10976,10 +10310,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3661</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -11004,10 +10336,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2449</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -11032,10 +10362,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>8210</t>
-        </is>
+      <c r="B18" t="n">
+        <v>8210</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -11060,10 +10388,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
+      <c r="B19" t="n">
+        <v>6515</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -11088,10 +10414,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
+      <c r="B20" t="n">
+        <v>3711</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -11116,10 +10440,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1303</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -11144,10 +10466,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B22" t="n">
+        <v>6805</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -11172,10 +10492,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>6139</t>
-        </is>
+      <c r="B23" t="n">
+        <v>6139</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -11200,10 +10518,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2454</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -11228,10 +10544,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>6488</t>
-        </is>
+      <c r="B25" t="n">
+        <v>6488</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -11256,10 +10570,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B26" t="n">
+        <v>6274</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -11284,10 +10596,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
+      <c r="B27" t="n">
+        <v>6669</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -11312,10 +10622,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
+      <c r="B28" t="n">
+        <v>2404</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -11340,10 +10648,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
+      <c r="B29" t="n">
+        <v>8358</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -11368,10 +10674,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3211</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3211</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -11396,10 +10700,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3189</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -11424,10 +10726,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>4979</t>
-        </is>
+      <c r="B32" t="n">
+        <v>4979</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -11452,10 +10752,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
+      <c r="B33" t="n">
+        <v>1326</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -11480,10 +10778,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
+      <c r="B34" t="n">
+        <v>1802</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -11508,10 +10804,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
+      <c r="B35" t="n">
+        <v>2408</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -11536,10 +10830,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>6191</t>
-        </is>
+      <c r="B36" t="n">
+        <v>6191</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -11564,10 +10856,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>3376</t>
-        </is>
+      <c r="B37" t="n">
+        <v>3376</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -11592,10 +10882,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
+      <c r="B38" t="n">
+        <v>8996</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -11620,10 +10908,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>3264</t>
-        </is>
+      <c r="B39" t="n">
+        <v>3264</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -11648,10 +10934,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>3533</t>
-        </is>
+      <c r="B40" t="n">
+        <v>3533</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -11676,10 +10960,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>3324</t>
-        </is>
+      <c r="B41" t="n">
+        <v>3324</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -11704,10 +10986,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
+      <c r="B42" t="n">
+        <v>1319</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -11732,10 +11012,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
+      <c r="B43" t="n">
+        <v>2002</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -11760,10 +11038,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>3217</t>
-        </is>
+      <c r="B44" t="n">
+        <v>3217</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -11788,10 +11064,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
+      <c r="B45" t="n">
+        <v>3008</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -11816,10 +11090,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
+      <c r="B46" t="n">
+        <v>2059</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -11844,10 +11116,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2357</t>
-        </is>
+      <c r="B47" t="n">
+        <v>2357</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -11872,10 +11142,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>1815</t>
-        </is>
+      <c r="B48" t="n">
+        <v>1815</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -11900,10 +11168,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2439</t>
-        </is>
+      <c r="B49" t="n">
+        <v>2439</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -11928,10 +11194,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
+      <c r="B50" t="n">
+        <v>8299</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -11956,10 +11220,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>3045</t>
-        </is>
+      <c r="B51" t="n">
+        <v>3045</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -11984,10 +11246,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>5536</t>
-        </is>
+      <c r="B52" t="n">
+        <v>5536</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -12012,10 +11272,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
+      <c r="B53" t="n">
+        <v>2313</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -12040,10 +11298,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>3583</t>
-        </is>
+      <c r="B54" t="n">
+        <v>3583</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -12068,10 +11324,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B55" t="n">
+        <v>2330</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -12100,10 +11354,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2382</t>
-        </is>
+      <c r="B56" t="n">
+        <v>2382</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -12132,10 +11384,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2881</t>
-        </is>
+      <c r="B57" t="n">
+        <v>2881</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -12164,10 +11414,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>3045</t>
-        </is>
+      <c r="B58" t="n">
+        <v>3045</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -12196,10 +11444,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
+      <c r="B59" t="n">
+        <v>2882</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -12228,10 +11474,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
+      <c r="B60" t="n">
+        <v>2891</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -12260,10 +11504,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2303</t>
-        </is>
+      <c r="B61" t="n">
+        <v>2303</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -12292,10 +11534,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
+      <c r="B62" t="n">
+        <v>2885</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -12324,10 +11564,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
+      <c r="B63" t="n">
+        <v>2880</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -12356,10 +11594,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
+      <c r="B64" t="n">
+        <v>2887</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -12388,10 +11624,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>3036</t>
-        </is>
+      <c r="B65" t="n">
+        <v>3036</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -12420,10 +11654,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
+      <c r="B66" t="n">
+        <v>2883</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -12452,10 +11684,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>4904</t>
-        </is>
+      <c r="B67" t="n">
+        <v>4904</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -12484,10 +11714,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
+      <c r="B68" t="n">
+        <v>1102</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -12516,10 +11744,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2379</t>
-        </is>
+      <c r="B69" t="n">
+        <v>2379</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -12548,10 +11774,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B70" t="n">
+        <v>3037</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -12580,10 +11804,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
+      <c r="B71" t="n">
+        <v>5274</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -12612,10 +11834,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2603</t>
-        </is>
+      <c r="B72" t="n">
+        <v>2603</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -12644,10 +11864,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>5289</t>
-        </is>
+      <c r="B73" t="n">
+        <v>5289</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -12676,10 +11894,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>1402</t>
-        </is>
+      <c r="B74" t="n">
+        <v>1402</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -12708,10 +11924,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2324</t>
-        </is>
+      <c r="B75" t="n">
+        <v>2324</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -12740,10 +11954,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>3264</t>
-        </is>
+      <c r="B76" t="n">
+        <v>3264</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -12772,10 +11984,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
+      <c r="B77" t="n">
+        <v>8299</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -12804,10 +12014,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2357</t>
-        </is>
+      <c r="B78" t="n">
+        <v>2357</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -12836,10 +12044,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B79" t="n">
+        <v>2383</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -12868,10 +12074,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
+      <c r="B80" t="n">
+        <v>3711</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -12900,10 +12104,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B81" t="n">
+        <v>2308</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -12932,10 +12134,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
+      <c r="B82" t="n">
+        <v>6515</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -12964,10 +12164,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>1560</t>
-        </is>
+      <c r="B83" t="n">
+        <v>1560</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -12996,10 +12194,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2912</t>
-        </is>
+      <c r="B84" t="n">
+        <v>2912</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -13028,10 +12224,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>9904</t>
-        </is>
+      <c r="B85" t="n">
+        <v>9904</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -13060,10 +12254,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>3260</t>
-        </is>
+      <c r="B86" t="n">
+        <v>3260</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -13092,10 +12284,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="B87" t="n">
+        <v>2360</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -13124,10 +12314,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
+      <c r="B88" t="n">
+        <v>2449</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -13156,10 +12344,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>8112</t>
-        </is>
+      <c r="B89" t="n">
+        <v>8112</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -13188,10 +12374,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>4938</t>
-        </is>
+      <c r="B90" t="n">
+        <v>4938</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -13220,10 +12404,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
+      <c r="B91" t="n">
+        <v>2618</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -13252,10 +12434,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
+      <c r="B92" t="n">
+        <v>1303</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -13284,10 +12464,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>6005</t>
-        </is>
+      <c r="B93" t="n">
+        <v>6005</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -13316,10 +12494,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>6446</t>
-        </is>
+      <c r="B94" t="n">
+        <v>6446</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -13348,10 +12524,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>3491</t>
-        </is>
+      <c r="B95" t="n">
+        <v>3491</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -13380,10 +12554,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
+      <c r="B96" t="n">
+        <v>2376</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13412,10 +12584,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>6691</t>
-        </is>
+      <c r="B97" t="n">
+        <v>6691</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13444,10 +12614,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>3105</t>
-        </is>
+      <c r="B98" t="n">
+        <v>3105</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -13476,10 +12644,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>8021</t>
-        </is>
+      <c r="B99" t="n">
+        <v>8021</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -13508,10 +12674,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>3702</t>
-        </is>
+      <c r="B100" t="n">
+        <v>3702</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13540,10 +12704,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>6239</t>
-        </is>
+      <c r="B101" t="n">
+        <v>6239</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13572,10 +12734,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>1785</t>
-        </is>
+      <c r="B102" t="n">
+        <v>1785</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13604,10 +12764,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2441</t>
-        </is>
+      <c r="B103" t="n">
+        <v>2441</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13636,10 +12794,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2610</t>
-        </is>
+      <c r="B104" t="n">
+        <v>2610</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13668,10 +12824,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>3006</t>
-        </is>
+      <c r="B105" t="n">
+        <v>3006</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13700,10 +12854,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B106" t="n">
+        <v>6223</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13732,10 +12884,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>1605</t>
-        </is>
+      <c r="B107" t="n">
+        <v>1605</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13764,10 +12914,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
+      <c r="B108" t="n">
+        <v>2313</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13796,10 +12944,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2467</t>
-        </is>
+      <c r="B109" t="n">
+        <v>2467</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13828,10 +12974,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>2486</t>
-        </is>
+      <c r="B110" t="n">
+        <v>2486</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13860,10 +13004,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
+      <c r="B111" t="n">
+        <v>3189</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13892,10 +13034,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
+      <c r="B112" t="n">
+        <v>6510</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13924,10 +13064,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>2474</t>
-        </is>
+      <c r="B113" t="n">
+        <v>2474</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13956,10 +13094,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>3081</t>
-        </is>
+      <c r="B114" t="n">
+        <v>3081</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13988,10 +13124,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
+      <c r="B115" t="n">
+        <v>3481</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14020,10 +13154,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
+      <c r="B116" t="n">
+        <v>2344</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14052,10 +13184,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>2385</t>
-        </is>
+      <c r="B117" t="n">
+        <v>2385</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14084,10 +13214,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
+      <c r="B118" t="n">
+        <v>2890</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14116,10 +13244,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>1815</t>
-        </is>
+      <c r="B119" t="n">
+        <v>1815</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14148,10 +13274,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>6282</t>
-        </is>
+      <c r="B120" t="n">
+        <v>6282</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14180,10 +13304,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>6290</t>
-        </is>
+      <c r="B121" t="n">
+        <v>6290</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14212,10 +13334,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
+      <c r="B122" t="n">
+        <v>6770</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14244,10 +13364,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>6903</t>
-        </is>
+      <c r="B123" t="n">
+        <v>6903</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14276,10 +13394,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
+      <c r="B124" t="n">
+        <v>8046</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14308,10 +13424,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>2492</t>
-        </is>
+      <c r="B125" t="n">
+        <v>2492</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14340,10 +13454,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>5234</t>
-        </is>
+      <c r="B126" t="n">
+        <v>5234</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14372,10 +13484,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>6548</t>
-        </is>
+      <c r="B127" t="n">
+        <v>6548</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14404,10 +13514,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>6257</t>
-        </is>
+      <c r="B128" t="n">
+        <v>6257</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14436,10 +13544,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>7795</t>
-        </is>
+      <c r="B129" t="n">
+        <v>7795</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14468,10 +13574,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
+      <c r="B130" t="n">
+        <v>1326</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14500,10 +13604,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
+      <c r="B131" t="n">
+        <v>1519</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14532,10 +13634,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B132" t="n">
+        <v>2345</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14564,10 +13664,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>3374</t>
-        </is>
+      <c r="B133" t="n">
+        <v>3374</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14596,10 +13694,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
+      <c r="B134" t="n">
+        <v>7769</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14628,10 +13724,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B135" t="n">
+        <v>2368</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14660,10 +13754,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>9910</t>
-        </is>
+      <c r="B136" t="n">
+        <v>9910</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14692,10 +13784,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>6442</t>
-        </is>
+      <c r="B137" t="n">
+        <v>6442</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14724,10 +13814,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>2851</t>
-        </is>
+      <c r="B138" t="n">
+        <v>2851</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14756,10 +13844,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
+      <c r="B139" t="n">
+        <v>2006</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14788,10 +13874,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>3010</t>
-        </is>
+      <c r="B140" t="n">
+        <v>3010</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14820,10 +13904,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>1227</t>
-        </is>
+      <c r="B141" t="n">
+        <v>1227</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14852,10 +13934,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>2501</t>
-        </is>
+      <c r="B142" t="n">
+        <v>2501</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -14884,10 +13964,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>2850</t>
-        </is>
+      <c r="B143" t="n">
+        <v>2850</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -14916,10 +13994,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>2897</t>
-        </is>
+      <c r="B144" t="n">
+        <v>2897</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -14948,10 +14024,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2903</t>
-        </is>
+      <c r="B145" t="n">
+        <v>2903</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -14980,10 +14054,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>8070</t>
-        </is>
+      <c r="B146" t="n">
+        <v>8070</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15012,10 +14084,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>2637</t>
-        </is>
+      <c r="B147" t="n">
+        <v>2637</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15044,10 +14114,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>2820</t>
-        </is>
+      <c r="B148" t="n">
+        <v>2820</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15076,10 +14144,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>2855</t>
-        </is>
+      <c r="B149" t="n">
+        <v>2855</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15108,10 +14174,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>3227</t>
-        </is>
+      <c r="B150" t="n">
+        <v>3227</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15140,10 +14204,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>9907</t>
-        </is>
+      <c r="B151" t="n">
+        <v>9907</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15172,10 +14234,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>1434</t>
-        </is>
+      <c r="B152" t="n">
+        <v>1434</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -15204,10 +14264,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
+      <c r="B153" t="n">
+        <v>3443</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -15236,10 +14294,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
+      <c r="B154" t="n">
+        <v>8358</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -15268,10 +14324,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B155" t="n">
+        <v>3017</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -15300,10 +14354,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
+      <c r="B156" t="n">
+        <v>2327</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -15332,10 +14384,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>6023</t>
-        </is>
+      <c r="B157" t="n">
+        <v>6023</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -15364,10 +14414,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B158" t="n">
+        <v>6274</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -15396,10 +14444,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>3005</t>
-        </is>
+      <c r="B159" t="n">
+        <v>3005</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -15428,10 +14474,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>2458</t>
-        </is>
+      <c r="B160" t="n">
+        <v>2458</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -15460,10 +14504,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
+      <c r="B161" t="n">
+        <v>2353</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -15492,10 +14534,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>6121</t>
-        </is>
+      <c r="B162" t="n">
+        <v>6121</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -15524,10 +14564,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>9917</t>
-        </is>
+      <c r="B163" t="n">
+        <v>9917</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -15556,10 +14594,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>2206</t>
-        </is>
+      <c r="B164" t="n">
+        <v>2206</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -15588,10 +14624,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>2352</t>
-        </is>
+      <c r="B165" t="n">
+        <v>2352</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -15620,10 +14654,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>2377</t>
-        </is>
+      <c r="B166" t="n">
+        <v>2377</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -15652,10 +14684,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>4766</t>
-        </is>
+      <c r="B167" t="n">
+        <v>4766</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -15684,10 +14714,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>6414</t>
-        </is>
+      <c r="B168" t="n">
+        <v>6414</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -15716,10 +14744,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>8415</t>
-        </is>
+      <c r="B169" t="n">
+        <v>8415</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -15748,10 +14774,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>9939</t>
-        </is>
+      <c r="B170" t="n">
+        <v>9939</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -15780,10 +14804,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>1795</t>
-        </is>
+      <c r="B171" t="n">
+        <v>1795</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -15812,10 +14834,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>6176</t>
-        </is>
+      <c r="B172" t="n">
+        <v>6176</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -15844,10 +14864,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B173" t="n">
+        <v>3653</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -15876,10 +14894,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B174" t="n">
+        <v>6805</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -15908,10 +14924,8 @@
           <t>00984A</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
+      <c r="B175" t="n">
+        <v>2301</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -15940,10 +14954,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>3036</t>
-        </is>
+      <c r="B176" t="n">
+        <v>3036</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -15972,10 +14984,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
+      <c r="B177" t="n">
+        <v>2412</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -16004,10 +15014,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B178" t="n">
+        <v>2330</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -16036,10 +15044,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>2303</t>
-        </is>
+      <c r="B179" t="n">
+        <v>2303</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -16068,10 +15074,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
+      <c r="B180" t="n">
+        <v>2454</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -16100,10 +15104,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>3044</t>
-        </is>
+      <c r="B181" t="n">
+        <v>3044</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -16132,10 +15134,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
+      <c r="B182" t="n">
+        <v>2344</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -16164,10 +15164,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>1590</t>
-        </is>
+      <c r="B183" t="n">
+        <v>1590</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -16196,10 +15194,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
+      <c r="B184" t="n">
+        <v>2327</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -16228,10 +15224,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B185" t="n">
+        <v>3037</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -16260,10 +15254,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="B186" t="n">
+        <v>2360</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -16292,10 +15284,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B187" t="n">
+        <v>2383</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -16324,10 +15314,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>3167</t>
-        </is>
+      <c r="B188" t="n">
+        <v>3167</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -16356,10 +15344,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
+      <c r="B189" t="n">
+        <v>8996</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -16388,10 +15374,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>3105</t>
-        </is>
+      <c r="B190" t="n">
+        <v>3105</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -16420,10 +15404,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
+      <c r="B191" t="n">
+        <v>6515</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -16452,10 +15434,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
+      <c r="B192" t="n">
+        <v>2313</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -16484,10 +15464,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B193" t="n">
+        <v>2368</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -16516,10 +15494,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
+      <c r="B194" t="n">
+        <v>2337</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -16548,10 +15524,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
+      <c r="B195" t="n">
+        <v>6770</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -16580,10 +15554,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>3533</t>
-        </is>
+      <c r="B196" t="n">
+        <v>3533</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -16612,10 +15584,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B197" t="n">
+        <v>2308</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -16644,10 +15614,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B198" t="n">
+        <v>3017</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -16676,10 +15644,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
+      <c r="B199" t="n">
+        <v>3481</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -16708,10 +15674,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>6285</t>
-        </is>
+      <c r="B200" t="n">
+        <v>6285</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -16740,10 +15704,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
+      <c r="B201" t="n">
+        <v>1303</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -16772,10 +15734,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B202" t="n">
+        <v>3653</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -16804,10 +15764,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B203" t="n">
+        <v>6223</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -16836,10 +15794,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B204" t="n">
+        <v>2345</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -16868,10 +15824,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
+      <c r="B205" t="n">
+        <v>2883</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -16900,10 +15854,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>1815</t>
-        </is>
+      <c r="B206" t="n">
+        <v>1815</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -16932,10 +15884,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>3324</t>
-        </is>
+      <c r="B207" t="n">
+        <v>3324</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -16964,10 +15914,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>3715</t>
-        </is>
+      <c r="B208" t="n">
+        <v>3715</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -16996,10 +15944,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>3264</t>
-        </is>
+      <c r="B209" t="n">
+        <v>3264</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -17028,10 +15974,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>3491</t>
-        </is>
+      <c r="B210" t="n">
+        <v>3491</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -17060,10 +16004,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B211" t="n">
+        <v>6805</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -17092,10 +16034,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
+      <c r="B212" t="n">
+        <v>8358</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -17124,10 +16064,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
+      <c r="B213" t="n">
+        <v>8299</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -17156,10 +16094,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>6290</t>
-        </is>
+      <c r="B214" t="n">
+        <v>6290</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -17188,10 +16124,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
+      <c r="B215" t="n">
+        <v>2882</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -17220,10 +16154,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B216" t="n">
+        <v>6274</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -17252,10 +16184,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>1560</t>
-        </is>
+      <c r="B217" t="n">
+        <v>1560</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -17284,10 +16214,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>6446</t>
-        </is>
+      <c r="B218" t="n">
+        <v>6446</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -17316,10 +16244,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>4722</t>
-        </is>
+      <c r="B219" t="n">
+        <v>4722</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -17348,10 +16274,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
+      <c r="B220" t="n">
+        <v>2449</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -17380,10 +16304,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>8021</t>
-        </is>
+      <c r="B221" t="n">
+        <v>8021</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -17412,10 +16334,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
+      <c r="B222" t="n">
+        <v>1519</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -17444,10 +16364,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
+      <c r="B223" t="n">
+        <v>5274</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -17476,10 +16394,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>6442</t>
-        </is>
+      <c r="B224" t="n">
+        <v>6442</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -17508,10 +16424,8 @@
           <t>00993A</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>7751</t>
-        </is>
+      <c r="B225" t="n">
+        <v>7751</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -18596,10 +17510,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B259" t="n">
+        <v>2330</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -18628,10 +17540,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B260" t="n">
+        <v>3017</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -18660,10 +17570,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
+      <c r="B261" t="n">
+        <v>8299</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -18692,10 +17600,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
+      <c r="B262" t="n">
+        <v>7769</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -18724,10 +17630,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B263" t="n">
+        <v>6223</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -18756,10 +17660,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B264" t="n">
+        <v>3653</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -18788,10 +17690,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B265" t="n">
+        <v>2308</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -18820,10 +17720,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B266" t="n">
+        <v>2345</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -18852,10 +17750,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
+      <c r="B267" t="n">
+        <v>2344</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -18884,10 +17780,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>3363</t>
-        </is>
+      <c r="B268" t="n">
+        <v>3363</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -18916,10 +17810,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B269" t="n">
+        <v>2368</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -18948,10 +17840,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B270" t="n">
+        <v>6274</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -18980,10 +17870,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
+      <c r="B271" t="n">
+        <v>8358</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -19012,10 +17900,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
+      <c r="B272" t="n">
+        <v>3665</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -19044,10 +17930,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B273" t="n">
+        <v>2383</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -19076,10 +17960,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B274" t="n">
+        <v>6805</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -19108,10 +17990,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B275" t="n">
+        <v>3037</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -19140,10 +18020,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
+      <c r="B276" t="n">
+        <v>3443</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -19172,10 +18050,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>6683</t>
-        </is>
+      <c r="B277" t="n">
+        <v>6683</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -19204,10 +18080,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
+      <c r="B278" t="n">
+        <v>2337</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -19236,10 +18110,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
+      <c r="B279" t="n">
+        <v>6510</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -19268,10 +18140,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="B280" t="n">
+        <v>2360</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -19300,10 +18170,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>2455</t>
-        </is>
+      <c r="B281" t="n">
+        <v>2455</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -19332,10 +18200,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
+      <c r="B282" t="n">
+        <v>6770</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -19364,10 +18230,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>5234</t>
-        </is>
+      <c r="B283" t="n">
+        <v>5234</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -19396,10 +18260,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B284" t="n">
+        <v>2308</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -19411,10 +18273,8 @@
           <t>31,500</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>4.34</t>
-        </is>
+      <c r="E284" t="n">
+        <v>4.34</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -19428,10 +18288,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
+      <c r="B285" t="n">
+        <v>2313</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -19443,10 +18301,8 @@
           <t>88,000</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
+      <c r="E285" t="n">
+        <v>1.99</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -19460,10 +18316,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B286" t="n">
+        <v>2330</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -19475,10 +18329,8 @@
           <t>106,999</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>19.16</t>
-        </is>
+      <c r="E286" t="n">
+        <v>19.16</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -19492,10 +18344,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B287" t="n">
+        <v>2345</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -19507,10 +18357,8 @@
           <t>32,000</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>4.46</t>
-        </is>
+      <c r="E287" t="n">
+        <v>4.46</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -19524,10 +18372,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="B288" t="n">
+        <v>2360</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -19539,10 +18385,8 @@
           <t>33,000</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>4.64</t>
-        </is>
+      <c r="E288" t="n">
+        <v>4.64</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -19556,10 +18400,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B289" t="n">
+        <v>2368</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -19571,10 +18413,8 @@
           <t>46,000</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>4.04</t>
-        </is>
+      <c r="E289" t="n">
+        <v>4.04</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -19588,10 +18428,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B290" t="n">
+        <v>2383</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -19603,10 +18441,8 @@
           <t>22,000</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>5.68</t>
-        </is>
+      <c r="E290" t="n">
+        <v>5.68</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -19620,10 +18456,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
+      <c r="B291" t="n">
+        <v>2408</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -19635,10 +18469,8 @@
           <t>62,000</t>
         </is>
       </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
+      <c r="E291" t="n">
+        <v>1.61</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -19652,10 +18484,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
+      <c r="B292" t="n">
+        <v>2449</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -19667,10 +18497,8 @@
           <t>87,000</t>
         </is>
       </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="E292" t="n">
+        <v>2.45</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -19684,10 +18512,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
+      <c r="B293" t="n">
+        <v>2454</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -19699,10 +18525,8 @@
           <t>1,000</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
+      <c r="E293" t="n">
+        <v>0.17</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -19716,10 +18540,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>2467</t>
-        </is>
+      <c r="B294" t="n">
+        <v>2467</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -19731,10 +18553,8 @@
           <t>20,000</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
+      <c r="E294" t="n">
+        <v>0.72</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -19748,10 +18568,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B295" t="n">
+        <v>3017</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -19763,10 +18581,8 @@
           <t>30,500</t>
         </is>
       </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>5.56</t>
-        </is>
+      <c r="E295" t="n">
+        <v>5.56</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -19780,10 +18596,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B296" t="n">
+        <v>3037</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -19795,10 +18609,8 @@
           <t>131,001</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>6.81</t>
-        </is>
+      <c r="E296" t="n">
+        <v>6.81</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -19812,10 +18624,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>3260</t>
-        </is>
+      <c r="B297" t="n">
+        <v>3260</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -19827,10 +18637,8 @@
           <t>44,000</t>
         </is>
       </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
+      <c r="E297" t="n">
+        <v>1.83</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -19844,10 +18652,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>3324</t>
-        </is>
+      <c r="B298" t="n">
+        <v>3324</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -19859,10 +18665,8 @@
           <t>4,000</t>
         </is>
       </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
+      <c r="E298" t="n">
+        <v>0.4</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -19876,10 +18680,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B299" t="n">
+        <v>3653</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -19891,10 +18693,8 @@
           <t>9,000</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>3.21</t>
-        </is>
+      <c r="E299" t="n">
+        <v>3.21</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -19908,10 +18708,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
+      <c r="B300" t="n">
+        <v>3665</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -19923,10 +18721,8 @@
           <t>13,000</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>2.16</t>
-        </is>
+      <c r="E300" t="n">
+        <v>2.16</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -19940,10 +18736,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
+      <c r="B301" t="n">
+        <v>3711</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -19955,10 +18749,8 @@
           <t>54,000</t>
         </is>
       </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
+      <c r="E301" t="n">
+        <v>1.77</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -19972,10 +18764,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>4904</t>
-        </is>
+      <c r="B302" t="n">
+        <v>4904</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -19987,10 +18777,8 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="E302" t="n">
+        <v>0</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -20004,10 +18792,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
+      <c r="B303" t="n">
+        <v>5274</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -20019,10 +18805,8 @@
           <t>3,600</t>
         </is>
       </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="E303" t="n">
+        <v>3.9</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -20036,10 +18820,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B304" t="n">
+        <v>6223</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -20051,10 +18833,8 @@
           <t>13,000</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>4.45</t>
-        </is>
+      <c r="E304" t="n">
+        <v>4.45</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -20068,10 +18848,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>6257</t>
-        </is>
+      <c r="B305" t="n">
+        <v>6257</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -20083,10 +18861,8 @@
           <t>45,000</t>
         </is>
       </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
+      <c r="E305" t="n">
+        <v>0.57</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -20100,10 +18876,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B306" t="n">
+        <v>6274</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -20115,10 +18889,8 @@
           <t>24,000</t>
         </is>
       </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
+      <c r="E306" t="n">
+        <v>1.16</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -20132,10 +18904,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>6442</t>
-        </is>
+      <c r="B307" t="n">
+        <v>6442</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -20147,10 +18917,8 @@
           <t>4,000</t>
         </is>
       </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
+      <c r="E307" t="n">
+        <v>0.65</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -20164,10 +18932,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
+      <c r="B308" t="n">
+        <v>6510</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -20179,10 +18945,8 @@
           <t>8,000</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>2.89</t>
-        </is>
+      <c r="E308" t="n">
+        <v>2.89</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -20196,10 +18960,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
+      <c r="B309" t="n">
+        <v>6515</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -20211,10 +18973,8 @@
           <t>8,100</t>
         </is>
       </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>5.13</t>
-        </is>
+      <c r="E309" t="n">
+        <v>5.13</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -20228,10 +18988,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B310" t="n">
+        <v>6805</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -20243,10 +19001,8 @@
           <t>17,001</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>2.84</t>
-        </is>
+      <c r="E310" t="n">
+        <v>2.84</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -20260,10 +19016,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
+      <c r="B311" t="n">
+        <v>7769</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -20275,10 +19029,8 @@
           <t>3,000</t>
         </is>
       </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
+      <c r="E311" t="n">
+        <v>1.21</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -20292,10 +19044,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
+      <c r="B312" t="n">
+        <v>8046</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -20307,10 +19057,8 @@
           <t>39,000</t>
         </is>
       </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
+      <c r="E312" t="n">
+        <v>2.03</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -20324,10 +19072,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
+      <c r="B313" t="n">
+        <v>8299</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -20339,10 +19085,8 @@
           <t>8,000</t>
         </is>
       </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
+      <c r="E313" t="n">
+        <v>1.49</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -20356,10 +19100,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
+      <c r="B314" t="n">
+        <v>8358</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -20371,10 +19113,8 @@
           <t>20,000</t>
         </is>
       </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
+      <c r="E314" t="n">
+        <v>0.5</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -20388,10 +19128,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
+      <c r="B315" t="n">
+        <v>8996</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -20403,10 +19141,8 @@
           <t>10,000</t>
         </is>
       </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
+      <c r="E315" t="n">
+        <v>0.88</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>

--- a/etf_holdings.xlsx
+++ b/etf_holdings.xlsx
@@ -1838,10 +1838,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B55" t="n">
+        <v>2330</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1866,10 +1864,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B56" t="n">
+        <v>2383</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1894,10 +1890,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B57" t="n">
+        <v>2308</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1922,10 +1916,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B58" t="n">
+        <v>3653</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1950,10 +1942,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B59" t="n">
+        <v>2368</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1978,10 +1968,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B60" t="n">
+        <v>6223</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -2006,10 +1994,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B61" t="n">
+        <v>2345</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -2034,10 +2020,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B62" t="n">
+        <v>3017</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2062,10 +2046,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B63" t="n">
+        <v>3037</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2090,10 +2072,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
+      <c r="B64" t="n">
+        <v>3665</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2118,10 +2098,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
+      <c r="B65" t="n">
+        <v>5274</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2146,10 +2124,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
+      <c r="B66" t="n">
+        <v>2327</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2174,10 +2150,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
+      <c r="B67" t="n">
+        <v>8046</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -2202,10 +2176,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
+      <c r="B68" t="n">
+        <v>2449</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -2230,10 +2202,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
+      <c r="B69" t="n">
+        <v>6510</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -2258,10 +2228,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
+      <c r="B70" t="n">
+        <v>3661</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -2286,10 +2254,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
+      <c r="B71" t="n">
+        <v>6515</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -2314,10 +2280,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
+      <c r="B72" t="n">
+        <v>3711</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -2342,10 +2306,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>8210</t>
-        </is>
+      <c r="B73" t="n">
+        <v>8210</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -2370,10 +2332,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
+      <c r="B74" t="n">
+        <v>1303</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -2398,10 +2358,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B75" t="n">
+        <v>6805</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -2426,10 +2384,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>6139</t>
-        </is>
+      <c r="B76" t="n">
+        <v>6139</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -2454,10 +2410,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
+      <c r="B77" t="n">
+        <v>2454</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -2482,10 +2436,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>6488</t>
-        </is>
+      <c r="B78" t="n">
+        <v>6488</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -2510,10 +2462,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B79" t="n">
+        <v>6274</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -2538,10 +2488,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
+      <c r="B80" t="n">
+        <v>2404</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -2566,10 +2514,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
+      <c r="B81" t="n">
+        <v>8358</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -2594,10 +2540,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>3211</t>
-        </is>
+      <c r="B82" t="n">
+        <v>3211</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -2622,10 +2566,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
+      <c r="B83" t="n">
+        <v>3189</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -2650,10 +2592,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
+      <c r="B84" t="n">
+        <v>1326</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -2678,10 +2618,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>4979</t>
-        </is>
+      <c r="B85" t="n">
+        <v>4979</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -2706,10 +2644,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
+      <c r="B86" t="n">
+        <v>1802</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -2734,10 +2670,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
+      <c r="B87" t="n">
+        <v>2408</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -2762,10 +2696,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>6191</t>
-        </is>
+      <c r="B88" t="n">
+        <v>6191</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -2790,10 +2722,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>3376</t>
-        </is>
+      <c r="B89" t="n">
+        <v>3376</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -2818,10 +2748,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
+      <c r="B90" t="n">
+        <v>8996</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -2846,10 +2774,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>3264</t>
-        </is>
+      <c r="B91" t="n">
+        <v>3264</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -2874,10 +2800,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
+      <c r="B92" t="n">
+        <v>6669</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -2902,10 +2826,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>5347</t>
-        </is>
+      <c r="B93" t="n">
+        <v>5347</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -2930,10 +2852,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>3533</t>
-        </is>
+      <c r="B94" t="n">
+        <v>3533</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -2958,10 +2878,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>3324</t>
-        </is>
+      <c r="B95" t="n">
+        <v>3324</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -2986,10 +2904,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
+      <c r="B96" t="n">
+        <v>1319</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -3014,10 +2930,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
+      <c r="B97" t="n">
+        <v>2002</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -3042,10 +2956,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>3217</t>
-        </is>
+      <c r="B98" t="n">
+        <v>3217</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -3070,10 +2982,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
+      <c r="B99" t="n">
+        <v>3008</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -3098,10 +3008,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
+      <c r="B100" t="n">
+        <v>2059</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -3126,10 +3034,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2357</t>
-        </is>
+      <c r="B101" t="n">
+        <v>2357</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -3154,10 +3060,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>1815</t>
-        </is>
+      <c r="B102" t="n">
+        <v>1815</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -3182,10 +3086,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2439</t>
-        </is>
+      <c r="B103" t="n">
+        <v>2439</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -3210,10 +3112,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
+      <c r="B104" t="n">
+        <v>8299</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -3238,10 +3138,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>3045</t>
-        </is>
+      <c r="B105" t="n">
+        <v>3045</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -3266,10 +3164,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>5536</t>
-        </is>
+      <c r="B106" t="n">
+        <v>5536</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -3294,10 +3190,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
+      <c r="B107" t="n">
+        <v>2313</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -3322,10 +3216,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>3583</t>
-        </is>
+      <c r="B108" t="n">
+        <v>3583</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11526,10 +11418,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B27" t="n">
+        <v>2330</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -11558,10 +11448,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3017</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -11590,10 +11478,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
+      <c r="B29" t="n">
+        <v>8299</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -11622,10 +11508,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B30" t="n">
+        <v>6223</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -11654,10 +11538,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3653</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -11686,10 +11568,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B32" t="n">
+        <v>6274</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -11718,10 +11598,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B33" t="n">
+        <v>2345</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -11750,10 +11628,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B34" t="n">
+        <v>2308</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -11782,10 +11658,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
+      <c r="B35" t="n">
+        <v>3665</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -11814,10 +11688,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
+      <c r="B36" t="n">
+        <v>2344</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -11846,10 +11718,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>3363</t>
-        </is>
+      <c r="B37" t="n">
+        <v>3363</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -11878,10 +11748,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
+      <c r="B38" t="n">
+        <v>3443</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -11910,10 +11778,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
+      <c r="B39" t="n">
+        <v>8358</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -11942,10 +11808,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B40" t="n">
+        <v>2368</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -11974,10 +11838,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B41" t="n">
+        <v>3037</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -12006,10 +11868,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B42" t="n">
+        <v>6805</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -12038,10 +11898,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B43" t="n">
+        <v>2383</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -12070,10 +11928,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>6683</t>
-        </is>
+      <c r="B44" t="n">
+        <v>6683</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -12102,10 +11958,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
+      <c r="B45" t="n">
+        <v>2337</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -12134,10 +11988,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
+      <c r="B46" t="n">
+        <v>7769</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -12166,10 +12018,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="B47" t="n">
+        <v>2360</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -12198,10 +12048,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
+      <c r="B48" t="n">
+        <v>6510</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -12230,10 +12078,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2455</t>
-        </is>
+      <c r="B49" t="n">
+        <v>2455</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -12262,10 +12108,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
+      <c r="B50" t="n">
+        <v>6770</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -12294,10 +12138,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>5234</t>
-        </is>
+      <c r="B51" t="n">
+        <v>5234</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -13268,10 +13110,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B34" t="n">
+        <v>2308</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -13283,10 +13123,8 @@
           <t>30,500</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>3.99</t>
-        </is>
+      <c r="E34" t="n">
+        <v>3.99</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -13300,10 +13138,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
+      <c r="B35" t="n">
+        <v>2313</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -13315,10 +13151,8 @@
           <t>88,000</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
+      <c r="E35" t="n">
+        <v>1.81</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -13332,10 +13166,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B36" t="n">
+        <v>2330</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -13347,10 +13179,8 @@
           <t>104,999</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>17.83</t>
-        </is>
+      <c r="E36" t="n">
+        <v>17.83</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -13364,10 +13194,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B37" t="n">
+        <v>2345</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -13379,10 +13207,8 @@
           <t>32,000</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>4.57</t>
-        </is>
+      <c r="E37" t="n">
+        <v>4.57</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -13396,10 +13222,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="B38" t="n">
+        <v>2360</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -13411,10 +13235,8 @@
           <t>33,000</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>4.61</t>
-        </is>
+      <c r="E38" t="n">
+        <v>4.61</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -13428,10 +13250,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B39" t="n">
+        <v>2368</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -13443,10 +13263,8 @@
           <t>43,000</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
+      <c r="E39" t="n">
+        <v>3.52</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -13460,10 +13278,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B40" t="n">
+        <v>2383</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -13475,10 +13291,8 @@
           <t>21,000</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>5.06</t>
-        </is>
+      <c r="E40" t="n">
+        <v>5.06</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -13492,10 +13306,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
+      <c r="B41" t="n">
+        <v>2408</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -13507,10 +13319,8 @@
           <t>62,000</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
+      <c r="E41" t="n">
+        <v>1.53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -13524,10 +13334,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
+      <c r="B42" t="n">
+        <v>2449</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -13539,10 +13347,8 @@
           <t>87,000</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
+      <c r="E42" t="n">
+        <v>2.51</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -13556,10 +13362,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2467</t>
-        </is>
+      <c r="B43" t="n">
+        <v>2467</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -13571,10 +13375,8 @@
           <t>20,000</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
+      <c r="E43" t="n">
+        <v>0.72</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -13588,10 +13390,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B44" t="n">
+        <v>3017</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -13603,10 +13403,8 @@
           <t>30,500</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>5.03</t>
-        </is>
+      <c r="E44" t="n">
+        <v>5.03</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -13620,10 +13418,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B45" t="n">
+        <v>3037</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -13635,10 +13431,8 @@
           <t>131,001</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>6.78</t>
-        </is>
+      <c r="E45" t="n">
+        <v>6.78</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -13652,10 +13446,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>3260</t>
-        </is>
+      <c r="B46" t="n">
+        <v>3260</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -13667,10 +13459,8 @@
           <t>44,000</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
+      <c r="E46" t="n">
+        <v>1.87</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -13684,10 +13474,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>3324</t>
-        </is>
+      <c r="B47" t="n">
+        <v>3324</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -13699,10 +13487,8 @@
           <t>4,000</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
+      <c r="E47" t="n">
+        <v>0.37</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -13716,10 +13502,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B48" t="n">
+        <v>3653</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -13731,10 +13515,8 @@
           <t>11,000</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>3.91</t>
-        </is>
+      <c r="E48" t="n">
+        <v>3.91</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -13748,10 +13530,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
+      <c r="B49" t="n">
+        <v>3661</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -13763,10 +13543,8 @@
           <t>1,500</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>0.44</t>
-        </is>
+      <c r="E49" t="n">
+        <v>0.44</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -13780,10 +13558,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
+      <c r="B50" t="n">
+        <v>3665</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -13795,10 +13571,8 @@
           <t>13,000</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
+      <c r="E50" t="n">
+        <v>1.96</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -13812,10 +13586,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
+      <c r="B51" t="n">
+        <v>3711</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -13827,10 +13599,8 @@
           <t>54,000</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
+      <c r="E51" t="n">
+        <v>1.72</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -13844,10 +13614,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>4904</t>
-        </is>
+      <c r="B52" t="n">
+        <v>4904</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -13859,10 +13627,8 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="E52" t="n">
+        <v>0</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -13876,10 +13642,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
+      <c r="B53" t="n">
+        <v>5274</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -13891,10 +13655,8 @@
           <t>3,600</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>3.97</t>
-        </is>
+      <c r="E53" t="n">
+        <v>3.97</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -13908,10 +13670,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B54" t="n">
+        <v>6223</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -13923,10 +13683,8 @@
           <t>13,000</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="E54" t="n">
+        <v>4.33</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -13940,10 +13698,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>6257</t>
-        </is>
+      <c r="B55" t="n">
+        <v>6257</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -13955,10 +13711,8 @@
           <t>45,000</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
+      <c r="E55" t="n">
+        <v>0.55</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -13972,10 +13726,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B56" t="n">
+        <v>6274</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -13987,10 +13739,8 @@
           <t>24,000</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
+      <c r="E56" t="n">
+        <v>1.14</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -14004,10 +13754,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>6442</t>
-        </is>
+      <c r="B57" t="n">
+        <v>6442</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -14019,10 +13767,8 @@
           <t>4,000</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
+      <c r="E57" t="n">
+        <v>0.66</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -14036,10 +13782,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>6488</t>
-        </is>
+      <c r="B58" t="n">
+        <v>6488</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -14051,10 +13795,8 @@
           <t>8,000</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
+      <c r="E58" t="n">
+        <v>0.34</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -14068,10 +13810,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
+      <c r="B59" t="n">
+        <v>6510</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -14083,10 +13823,8 @@
           <t>8,000</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2.67</t>
-        </is>
+      <c r="E59" t="n">
+        <v>2.67</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -14100,10 +13838,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
+      <c r="B60" t="n">
+        <v>6515</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -14115,10 +13851,8 @@
           <t>8,100</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>5.22</t>
-        </is>
+      <c r="E60" t="n">
+        <v>5.22</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -14132,10 +13866,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B61" t="n">
+        <v>6805</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -14147,10 +13879,8 @@
           <t>17,001</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>2.79</t>
-        </is>
+      <c r="E61" t="n">
+        <v>2.79</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -14164,10 +13894,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
+      <c r="B62" t="n">
+        <v>7769</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -14179,10 +13907,8 @@
           <t>3,000</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
+      <c r="E62" t="n">
+        <v>1.17</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -14196,10 +13922,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
+      <c r="B63" t="n">
+        <v>8046</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -14211,10 +13935,8 @@
           <t>39,000</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
+      <c r="E63" t="n">
+        <v>1.97</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -14228,10 +13950,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
+      <c r="B64" t="n">
+        <v>8299</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -14243,10 +13963,8 @@
           <t>8,000</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
+      <c r="E64" t="n">
+        <v>1.41</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -14260,10 +13978,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
+      <c r="B65" t="n">
+        <v>8358</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -14275,10 +13991,8 @@
           <t>20,000</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
+      <c r="E65" t="n">
+        <v>0.49</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -14292,10 +14006,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
+      <c r="B66" t="n">
+        <v>8996</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -14307,10 +14019,8 @@
           <t>10,000</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
+      <c r="E66" t="n">
+        <v>0.85</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -15748,10 +15458,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B55" t="n">
+        <v>2330</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -15776,10 +15484,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B56" t="n">
+        <v>2383</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -15804,10 +15510,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B57" t="n">
+        <v>2308</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -15832,10 +15536,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B58" t="n">
+        <v>3653</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -15860,10 +15562,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B59" t="n">
+        <v>2368</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -15888,10 +15588,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B60" t="n">
+        <v>6223</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -15916,10 +15614,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B61" t="n">
+        <v>2345</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -15944,10 +15640,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B62" t="n">
+        <v>3017</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -15972,10 +15666,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B63" t="n">
+        <v>3037</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -16000,10 +15692,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
+      <c r="B64" t="n">
+        <v>3665</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -16028,10 +15718,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
+      <c r="B65" t="n">
+        <v>5274</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -16056,10 +15744,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
+      <c r="B66" t="n">
+        <v>2327</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -16084,10 +15770,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
+      <c r="B67" t="n">
+        <v>8046</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -16112,10 +15796,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
+      <c r="B68" t="n">
+        <v>2449</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -16140,10 +15822,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
+      <c r="B69" t="n">
+        <v>6510</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -16168,10 +15848,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
+      <c r="B70" t="n">
+        <v>3661</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -16196,10 +15874,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
+      <c r="B71" t="n">
+        <v>6515</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -16224,10 +15900,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
+      <c r="B72" t="n">
+        <v>3711</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -16252,10 +15926,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>8210</t>
-        </is>
+      <c r="B73" t="n">
+        <v>8210</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -16280,10 +15952,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
+      <c r="B74" t="n">
+        <v>1303</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -16308,10 +15978,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B75" t="n">
+        <v>6805</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -16336,10 +16004,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>6139</t>
-        </is>
+      <c r="B76" t="n">
+        <v>6139</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -16364,10 +16030,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
+      <c r="B77" t="n">
+        <v>2454</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -16392,10 +16056,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>6488</t>
-        </is>
+      <c r="B78" t="n">
+        <v>6488</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -16420,10 +16082,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B79" t="n">
+        <v>6274</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -16448,10 +16108,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
+      <c r="B80" t="n">
+        <v>2404</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -16476,10 +16134,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
+      <c r="B81" t="n">
+        <v>8358</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -16504,10 +16160,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>3211</t>
-        </is>
+      <c r="B82" t="n">
+        <v>3211</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -16532,10 +16186,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
+      <c r="B83" t="n">
+        <v>3189</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -16560,10 +16212,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
+      <c r="B84" t="n">
+        <v>1326</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -16588,10 +16238,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>4979</t>
-        </is>
+      <c r="B85" t="n">
+        <v>4979</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -16616,10 +16264,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
+      <c r="B86" t="n">
+        <v>1802</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -16644,10 +16290,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
+      <c r="B87" t="n">
+        <v>2408</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -16672,10 +16316,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>6191</t>
-        </is>
+      <c r="B88" t="n">
+        <v>6191</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -16700,10 +16342,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>3376</t>
-        </is>
+      <c r="B89" t="n">
+        <v>3376</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -16728,10 +16368,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
+      <c r="B90" t="n">
+        <v>8996</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -16756,10 +16394,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>3264</t>
-        </is>
+      <c r="B91" t="n">
+        <v>3264</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -16784,10 +16420,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
+      <c r="B92" t="n">
+        <v>6669</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -16812,10 +16446,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>5347</t>
-        </is>
+      <c r="B93" t="n">
+        <v>5347</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -16840,10 +16472,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>3533</t>
-        </is>
+      <c r="B94" t="n">
+        <v>3533</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -16868,10 +16498,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>3324</t>
-        </is>
+      <c r="B95" t="n">
+        <v>3324</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -16896,10 +16524,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
+      <c r="B96" t="n">
+        <v>1319</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -16924,10 +16550,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
+      <c r="B97" t="n">
+        <v>2002</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -16952,10 +16576,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>3217</t>
-        </is>
+      <c r="B98" t="n">
+        <v>3217</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -16980,10 +16602,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
+      <c r="B99" t="n">
+        <v>3008</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -17008,10 +16628,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
+      <c r="B100" t="n">
+        <v>2059</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -17036,10 +16654,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2357</t>
-        </is>
+      <c r="B101" t="n">
+        <v>2357</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -17064,10 +16680,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>1815</t>
-        </is>
+      <c r="B102" t="n">
+        <v>1815</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -17092,10 +16706,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2439</t>
-        </is>
+      <c r="B103" t="n">
+        <v>2439</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -17120,10 +16732,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
+      <c r="B104" t="n">
+        <v>8299</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -17148,10 +16758,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>3045</t>
-        </is>
+      <c r="B105" t="n">
+        <v>3045</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -17176,10 +16784,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>5536</t>
-        </is>
+      <c r="B106" t="n">
+        <v>5536</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -17204,10 +16810,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
+      <c r="B107" t="n">
+        <v>2313</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -17232,10 +16836,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>3583</t>
-        </is>
+      <c r="B108" t="n">
+        <v>3583</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -25252,10 +24854,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B371" t="n">
+        <v>2330</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
@@ -25284,10 +24884,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B372" t="n">
+        <v>3017</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
@@ -25316,10 +24914,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
+      <c r="B373" t="n">
+        <v>8299</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
@@ -25348,10 +24944,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B374" t="n">
+        <v>6223</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
@@ -25380,10 +24974,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B375" t="n">
+        <v>3653</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
@@ -25412,10 +25004,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B376" t="n">
+        <v>6274</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
@@ -25444,10 +25034,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B377" t="n">
+        <v>2345</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
@@ -25476,10 +25064,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B378" t="n">
+        <v>2308</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
@@ -25508,10 +25094,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
+      <c r="B379" t="n">
+        <v>3665</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
@@ -25540,10 +25124,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
+      <c r="B380" t="n">
+        <v>2344</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
@@ -25572,10 +25154,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>3363</t>
-        </is>
+      <c r="B381" t="n">
+        <v>3363</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -25604,10 +25184,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
+      <c r="B382" t="n">
+        <v>3443</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
@@ -25636,10 +25214,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
+      <c r="B383" t="n">
+        <v>8358</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
@@ -25668,10 +25244,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B384" t="n">
+        <v>2368</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
@@ -25700,10 +25274,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B385" t="n">
+        <v>3037</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -25732,10 +25304,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B386" t="n">
+        <v>6805</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -25764,10 +25334,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B387" t="n">
+        <v>2383</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -25796,10 +25364,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>6683</t>
-        </is>
+      <c r="B388" t="n">
+        <v>6683</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -25828,10 +25394,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
+      <c r="B389" t="n">
+        <v>2337</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
@@ -25860,10 +25424,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
+      <c r="B390" t="n">
+        <v>7769</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
@@ -25892,10 +25454,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="B391" t="n">
+        <v>2360</v>
       </c>
       <c r="C391" t="inlineStr">
         <is>
@@ -25924,10 +25484,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
+      <c r="B392" t="n">
+        <v>6510</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
@@ -25956,10 +25514,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>2455</t>
-        </is>
+      <c r="B393" t="n">
+        <v>2455</v>
       </c>
       <c r="C393" t="inlineStr">
         <is>
@@ -25988,10 +25544,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
+      <c r="B394" t="n">
+        <v>6770</v>
       </c>
       <c r="C394" t="inlineStr">
         <is>
@@ -26020,10 +25574,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>5234</t>
-        </is>
+      <c r="B395" t="n">
+        <v>5234</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
@@ -26948,10 +26500,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B428" t="n">
+        <v>2308</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
@@ -26963,10 +26513,8 @@
           <t>30,500</t>
         </is>
       </c>
-      <c r="E428" t="inlineStr">
-        <is>
-          <t>3.99</t>
-        </is>
+      <c r="E428" t="n">
+        <v>3.99</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -26980,10 +26528,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
+      <c r="B429" t="n">
+        <v>2313</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
@@ -26995,10 +26541,8 @@
           <t>88,000</t>
         </is>
       </c>
-      <c r="E429" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
+      <c r="E429" t="n">
+        <v>1.81</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -27012,10 +26556,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B430" t="n">
+        <v>2330</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
@@ -27027,10 +26569,8 @@
           <t>104,999</t>
         </is>
       </c>
-      <c r="E430" t="inlineStr">
-        <is>
-          <t>17.83</t>
-        </is>
+      <c r="E430" t="n">
+        <v>17.83</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -27044,10 +26584,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B431" t="n">
+        <v>2345</v>
       </c>
       <c r="C431" t="inlineStr">
         <is>
@@ -27059,10 +26597,8 @@
           <t>32,000</t>
         </is>
       </c>
-      <c r="E431" t="inlineStr">
-        <is>
-          <t>4.57</t>
-        </is>
+      <c r="E431" t="n">
+        <v>4.57</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -27076,10 +26612,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="B432" t="n">
+        <v>2360</v>
       </c>
       <c r="C432" t="inlineStr">
         <is>
@@ -27091,10 +26625,8 @@
           <t>33,000</t>
         </is>
       </c>
-      <c r="E432" t="inlineStr">
-        <is>
-          <t>4.61</t>
-        </is>
+      <c r="E432" t="n">
+        <v>4.61</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -27108,10 +26640,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B433" t="n">
+        <v>2368</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
@@ -27123,10 +26653,8 @@
           <t>43,000</t>
         </is>
       </c>
-      <c r="E433" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
+      <c r="E433" t="n">
+        <v>3.52</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -27140,10 +26668,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B434" t="n">
+        <v>2383</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
@@ -27155,10 +26681,8 @@
           <t>21,000</t>
         </is>
       </c>
-      <c r="E434" t="inlineStr">
-        <is>
-          <t>5.06</t>
-        </is>
+      <c r="E434" t="n">
+        <v>5.06</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -27172,10 +26696,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
+      <c r="B435" t="n">
+        <v>2408</v>
       </c>
       <c r="C435" t="inlineStr">
         <is>
@@ -27187,10 +26709,8 @@
           <t>62,000</t>
         </is>
       </c>
-      <c r="E435" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
+      <c r="E435" t="n">
+        <v>1.53</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -27204,10 +26724,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
+      <c r="B436" t="n">
+        <v>2449</v>
       </c>
       <c r="C436" t="inlineStr">
         <is>
@@ -27219,10 +26737,8 @@
           <t>87,000</t>
         </is>
       </c>
-      <c r="E436" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
+      <c r="E436" t="n">
+        <v>2.51</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -27236,10 +26752,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>2467</t>
-        </is>
+      <c r="B437" t="n">
+        <v>2467</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
@@ -27251,10 +26765,8 @@
           <t>20,000</t>
         </is>
       </c>
-      <c r="E437" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
+      <c r="E437" t="n">
+        <v>0.72</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -27268,10 +26780,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B438" t="n">
+        <v>3017</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
@@ -27283,10 +26793,8 @@
           <t>30,500</t>
         </is>
       </c>
-      <c r="E438" t="inlineStr">
-        <is>
-          <t>5.03</t>
-        </is>
+      <c r="E438" t="n">
+        <v>5.03</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -27300,10 +26808,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B439" t="n">
+        <v>3037</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
@@ -27315,10 +26821,8 @@
           <t>131,001</t>
         </is>
       </c>
-      <c r="E439" t="inlineStr">
-        <is>
-          <t>6.78</t>
-        </is>
+      <c r="E439" t="n">
+        <v>6.78</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -27332,10 +26836,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>3260</t>
-        </is>
+      <c r="B440" t="n">
+        <v>3260</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
@@ -27347,10 +26849,8 @@
           <t>44,000</t>
         </is>
       </c>
-      <c r="E440" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
+      <c r="E440" t="n">
+        <v>1.87</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -27364,10 +26864,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>3324</t>
-        </is>
+      <c r="B441" t="n">
+        <v>3324</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
@@ -27379,10 +26877,8 @@
           <t>4,000</t>
         </is>
       </c>
-      <c r="E441" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
+      <c r="E441" t="n">
+        <v>0.37</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -27396,10 +26892,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B442" t="n">
+        <v>3653</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
@@ -27411,10 +26905,8 @@
           <t>11,000</t>
         </is>
       </c>
-      <c r="E442" t="inlineStr">
-        <is>
-          <t>3.91</t>
-        </is>
+      <c r="E442" t="n">
+        <v>3.91</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -27428,10 +26920,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
+      <c r="B443" t="n">
+        <v>3661</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
@@ -27443,10 +26933,8 @@
           <t>1,500</t>
         </is>
       </c>
-      <c r="E443" t="inlineStr">
-        <is>
-          <t>0.44</t>
-        </is>
+      <c r="E443" t="n">
+        <v>0.44</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -27460,10 +26948,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
+      <c r="B444" t="n">
+        <v>3665</v>
       </c>
       <c r="C444" t="inlineStr">
         <is>
@@ -27475,10 +26961,8 @@
           <t>13,000</t>
         </is>
       </c>
-      <c r="E444" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
+      <c r="E444" t="n">
+        <v>1.96</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -27492,10 +26976,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
+      <c r="B445" t="n">
+        <v>3711</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
@@ -27507,10 +26989,8 @@
           <t>54,000</t>
         </is>
       </c>
-      <c r="E445" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
+      <c r="E445" t="n">
+        <v>1.72</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -27524,10 +27004,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>4904</t>
-        </is>
+      <c r="B446" t="n">
+        <v>4904</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
@@ -27539,10 +27017,8 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E446" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="E446" t="n">
+        <v>0</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -27556,10 +27032,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
+      <c r="B447" t="n">
+        <v>5274</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
@@ -27571,10 +27045,8 @@
           <t>3,600</t>
         </is>
       </c>
-      <c r="E447" t="inlineStr">
-        <is>
-          <t>3.97</t>
-        </is>
+      <c r="E447" t="n">
+        <v>3.97</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -27588,10 +27060,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B448" t="n">
+        <v>6223</v>
       </c>
       <c r="C448" t="inlineStr">
         <is>
@@ -27603,10 +27073,8 @@
           <t>13,000</t>
         </is>
       </c>
-      <c r="E448" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="E448" t="n">
+        <v>4.33</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -27620,10 +27088,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>6257</t>
-        </is>
+      <c r="B449" t="n">
+        <v>6257</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
@@ -27635,10 +27101,8 @@
           <t>45,000</t>
         </is>
       </c>
-      <c r="E449" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
+      <c r="E449" t="n">
+        <v>0.55</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -27652,10 +27116,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B450" t="n">
+        <v>6274</v>
       </c>
       <c r="C450" t="inlineStr">
         <is>
@@ -27667,10 +27129,8 @@
           <t>24,000</t>
         </is>
       </c>
-      <c r="E450" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
+      <c r="E450" t="n">
+        <v>1.14</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -27684,10 +27144,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>6442</t>
-        </is>
+      <c r="B451" t="n">
+        <v>6442</v>
       </c>
       <c r="C451" t="inlineStr">
         <is>
@@ -27699,10 +27157,8 @@
           <t>4,000</t>
         </is>
       </c>
-      <c r="E451" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
+      <c r="E451" t="n">
+        <v>0.66</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -27716,10 +27172,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>6488</t>
-        </is>
+      <c r="B452" t="n">
+        <v>6488</v>
       </c>
       <c r="C452" t="inlineStr">
         <is>
@@ -27731,10 +27185,8 @@
           <t>8,000</t>
         </is>
       </c>
-      <c r="E452" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
+      <c r="E452" t="n">
+        <v>0.34</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -27748,10 +27200,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
+      <c r="B453" t="n">
+        <v>6510</v>
       </c>
       <c r="C453" t="inlineStr">
         <is>
@@ -27763,10 +27213,8 @@
           <t>8,000</t>
         </is>
       </c>
-      <c r="E453" t="inlineStr">
-        <is>
-          <t>2.67</t>
-        </is>
+      <c r="E453" t="n">
+        <v>2.67</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -27780,10 +27228,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
+      <c r="B454" t="n">
+        <v>6515</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
@@ -27795,10 +27241,8 @@
           <t>8,100</t>
         </is>
       </c>
-      <c r="E454" t="inlineStr">
-        <is>
-          <t>5.22</t>
-        </is>
+      <c r="E454" t="n">
+        <v>5.22</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -27812,10 +27256,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B455" t="n">
+        <v>6805</v>
       </c>
       <c r="C455" t="inlineStr">
         <is>
@@ -27827,10 +27269,8 @@
           <t>17,001</t>
         </is>
       </c>
-      <c r="E455" t="inlineStr">
-        <is>
-          <t>2.79</t>
-        </is>
+      <c r="E455" t="n">
+        <v>2.79</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -27844,10 +27284,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
+      <c r="B456" t="n">
+        <v>7769</v>
       </c>
       <c r="C456" t="inlineStr">
         <is>
@@ -27859,10 +27297,8 @@
           <t>3,000</t>
         </is>
       </c>
-      <c r="E456" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
+      <c r="E456" t="n">
+        <v>1.17</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -27876,10 +27312,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
+      <c r="B457" t="n">
+        <v>8046</v>
       </c>
       <c r="C457" t="inlineStr">
         <is>
@@ -27891,10 +27325,8 @@
           <t>39,000</t>
         </is>
       </c>
-      <c r="E457" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
+      <c r="E457" t="n">
+        <v>1.97</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -27908,10 +27340,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
+      <c r="B458" t="n">
+        <v>8299</v>
       </c>
       <c r="C458" t="inlineStr">
         <is>
@@ -27923,10 +27353,8 @@
           <t>8,000</t>
         </is>
       </c>
-      <c r="E458" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
+      <c r="E458" t="n">
+        <v>1.41</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -27940,10 +27368,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B459" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
+      <c r="B459" t="n">
+        <v>8358</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
@@ -27955,10 +27381,8 @@
           <t>20,000</t>
         </is>
       </c>
-      <c r="E459" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
+      <c r="E459" t="n">
+        <v>0.49</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -27972,10 +27396,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
+      <c r="B460" t="n">
+        <v>8996</v>
       </c>
       <c r="C460" t="inlineStr">
         <is>
@@ -27987,10 +27409,8 @@
           <t>10,000</t>
         </is>
       </c>
-      <c r="E460" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
+      <c r="E460" t="n">
+        <v>0.85</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>

--- a/etf_holdings.xlsx
+++ b/etf_holdings.xlsx
@@ -17812,10 +17812,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B77" t="n">
+        <v>2330</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -17844,10 +17842,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B78" t="n">
+        <v>3017</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -17876,10 +17872,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
+      <c r="B79" t="n">
+        <v>8299</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -17908,10 +17902,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B80" t="n">
+        <v>6223</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -17940,10 +17932,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B81" t="n">
+        <v>6274</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -17972,10 +17962,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
+      <c r="B82" t="n">
+        <v>3665</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -18004,10 +17992,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B83" t="n">
+        <v>3653</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -18036,10 +18022,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>3363</t>
-        </is>
+      <c r="B84" t="n">
+        <v>3363</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -18068,10 +18052,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B85" t="n">
+        <v>2345</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -18100,10 +18082,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B86" t="n">
+        <v>2308</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -18132,10 +18112,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
+      <c r="B87" t="n">
+        <v>3443</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -18164,10 +18142,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B88" t="n">
+        <v>2368</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -18196,10 +18172,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B89" t="n">
+        <v>6805</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -18228,10 +18202,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
+      <c r="B90" t="n">
+        <v>2337</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -18260,10 +18232,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B91" t="n">
+        <v>2383</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -18292,10 +18262,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>6683</t>
-        </is>
+      <c r="B92" t="n">
+        <v>6683</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -18324,10 +18292,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B93" t="n">
+        <v>3037</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -18356,10 +18322,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
+      <c r="B94" t="n">
+        <v>8358</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -18388,10 +18352,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
+      <c r="B95" t="n">
+        <v>2344</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -18420,10 +18382,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="B96" t="n">
+        <v>2360</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -18452,10 +18412,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
+      <c r="B97" t="n">
+        <v>6510</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -18484,10 +18442,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2455</t>
-        </is>
+      <c r="B98" t="n">
+        <v>2455</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -18516,10 +18472,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
+      <c r="B99" t="n">
+        <v>7769</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -18548,10 +18502,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
+      <c r="B100" t="n">
+        <v>6770</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -18580,10 +18532,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>5234</t>
-        </is>
+      <c r="B101" t="n">
+        <v>5234</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -39680,10 +39630,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B594" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B594" t="n">
+        <v>2330</v>
       </c>
       <c r="C594" t="inlineStr">
         <is>
@@ -39712,10 +39660,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B595" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B595" t="n">
+        <v>3017</v>
       </c>
       <c r="C595" t="inlineStr">
         <is>
@@ -39744,10 +39690,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B596" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
+      <c r="B596" t="n">
+        <v>8299</v>
       </c>
       <c r="C596" t="inlineStr">
         <is>
@@ -39776,10 +39720,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B597" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B597" t="n">
+        <v>6223</v>
       </c>
       <c r="C597" t="inlineStr">
         <is>
@@ -39808,10 +39750,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B598" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B598" t="n">
+        <v>6274</v>
       </c>
       <c r="C598" t="inlineStr">
         <is>
@@ -39840,10 +39780,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B599" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
+      <c r="B599" t="n">
+        <v>3665</v>
       </c>
       <c r="C599" t="inlineStr">
         <is>
@@ -39872,10 +39810,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B600" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B600" t="n">
+        <v>3653</v>
       </c>
       <c r="C600" t="inlineStr">
         <is>
@@ -39904,10 +39840,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B601" t="inlineStr">
-        <is>
-          <t>3363</t>
-        </is>
+      <c r="B601" t="n">
+        <v>3363</v>
       </c>
       <c r="C601" t="inlineStr">
         <is>
@@ -39936,10 +39870,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B602" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B602" t="n">
+        <v>2345</v>
       </c>
       <c r="C602" t="inlineStr">
         <is>
@@ -39968,10 +39900,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B603" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B603" t="n">
+        <v>2308</v>
       </c>
       <c r="C603" t="inlineStr">
         <is>
@@ -40000,10 +39930,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B604" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
+      <c r="B604" t="n">
+        <v>3443</v>
       </c>
       <c r="C604" t="inlineStr">
         <is>
@@ -40032,10 +39960,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B605" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B605" t="n">
+        <v>2368</v>
       </c>
       <c r="C605" t="inlineStr">
         <is>
@@ -40064,10 +39990,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B606" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B606" t="n">
+        <v>6805</v>
       </c>
       <c r="C606" t="inlineStr">
         <is>
@@ -40096,10 +40020,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B607" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
+      <c r="B607" t="n">
+        <v>2337</v>
       </c>
       <c r="C607" t="inlineStr">
         <is>
@@ -40128,10 +40050,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B608" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B608" t="n">
+        <v>2383</v>
       </c>
       <c r="C608" t="inlineStr">
         <is>
@@ -40160,10 +40080,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B609" t="inlineStr">
-        <is>
-          <t>6683</t>
-        </is>
+      <c r="B609" t="n">
+        <v>6683</v>
       </c>
       <c r="C609" t="inlineStr">
         <is>
@@ -40192,10 +40110,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B610" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B610" t="n">
+        <v>3037</v>
       </c>
       <c r="C610" t="inlineStr">
         <is>
@@ -40224,10 +40140,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B611" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
+      <c r="B611" t="n">
+        <v>8358</v>
       </c>
       <c r="C611" t="inlineStr">
         <is>
@@ -40256,10 +40170,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B612" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
+      <c r="B612" t="n">
+        <v>2344</v>
       </c>
       <c r="C612" t="inlineStr">
         <is>
@@ -40288,10 +40200,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B613" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="B613" t="n">
+        <v>2360</v>
       </c>
       <c r="C613" t="inlineStr">
         <is>
@@ -40320,10 +40230,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B614" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
+      <c r="B614" t="n">
+        <v>6510</v>
       </c>
       <c r="C614" t="inlineStr">
         <is>
@@ -40352,10 +40260,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B615" t="inlineStr">
-        <is>
-          <t>2455</t>
-        </is>
+      <c r="B615" t="n">
+        <v>2455</v>
       </c>
       <c r="C615" t="inlineStr">
         <is>
@@ -40384,10 +40290,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B616" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
+      <c r="B616" t="n">
+        <v>7769</v>
       </c>
       <c r="C616" t="inlineStr">
         <is>
@@ -40416,10 +40320,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B617" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
+      <c r="B617" t="n">
+        <v>6770</v>
       </c>
       <c r="C617" t="inlineStr">
         <is>
@@ -40448,10 +40350,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B618" t="inlineStr">
-        <is>
-          <t>5234</t>
-        </is>
+      <c r="B618" t="n">
+        <v>5234</v>
       </c>
       <c r="C618" t="inlineStr">
         <is>

--- a/etf_holdings.xlsx
+++ b/etf_holdings.xlsx
@@ -11458,10 +11458,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B425" t="n">
+        <v>2330</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
@@ -11486,10 +11484,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B426" t="n">
+        <v>2383</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
@@ -11514,10 +11510,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B427" t="n">
+        <v>2308</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
@@ -11542,10 +11536,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B428" t="n">
+        <v>3017</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
@@ -11570,10 +11562,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B429" t="n">
+        <v>3653</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
@@ -11598,10 +11588,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B430" t="n">
+        <v>2345</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
@@ -11626,10 +11614,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B431" t="n">
+        <v>2368</v>
       </c>
       <c r="C431" t="inlineStr">
         <is>
@@ -11654,10 +11640,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
+      <c r="B432" t="n">
+        <v>3665</v>
       </c>
       <c r="C432" t="inlineStr">
         <is>
@@ -11682,10 +11666,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B433" t="n">
+        <v>6223</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
@@ -11710,10 +11692,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B434" t="n">
+        <v>3037</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
@@ -11738,10 +11718,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
+      <c r="B435" t="n">
+        <v>8046</v>
       </c>
       <c r="C435" t="inlineStr">
         <is>
@@ -11766,10 +11744,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
+      <c r="B436" t="n">
+        <v>5274</v>
       </c>
       <c r="C436" t="inlineStr">
         <is>
@@ -11794,10 +11770,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
+      <c r="B437" t="n">
+        <v>2327</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
@@ -11822,10 +11796,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
+      <c r="B438" t="n">
+        <v>3711</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
@@ -11850,10 +11822,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
+      <c r="B439" t="n">
+        <v>6515</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
@@ -11878,10 +11848,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
+      <c r="B440" t="n">
+        <v>2449</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
@@ -11906,10 +11874,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
+      <c r="B441" t="n">
+        <v>6510</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
@@ -11934,10 +11900,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>3211</t>
-        </is>
+      <c r="B442" t="n">
+        <v>3211</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
@@ -11962,10 +11926,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>8210</t>
-        </is>
+      <c r="B443" t="n">
+        <v>8210</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
@@ -11990,10 +11952,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B444" t="n">
+        <v>6805</v>
       </c>
       <c r="C444" t="inlineStr">
         <is>
@@ -12018,10 +11978,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
+      <c r="B445" t="n">
+        <v>1303</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
@@ -12046,10 +12004,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
+      <c r="B446" t="n">
+        <v>3661</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
@@ -12074,10 +12030,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
+      <c r="B447" t="n">
+        <v>3189</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
@@ -12102,10 +12056,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>6139</t>
-        </is>
+      <c r="B448" t="n">
+        <v>6139</v>
       </c>
       <c r="C448" t="inlineStr">
         <is>
@@ -12130,10 +12082,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
+      <c r="B449" t="n">
+        <v>2454</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
@@ -12158,10 +12108,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>6488</t>
-        </is>
+      <c r="B450" t="n">
+        <v>6488</v>
       </c>
       <c r="C450" t="inlineStr">
         <is>
@@ -12186,10 +12134,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>5347</t>
-        </is>
+      <c r="B451" t="n">
+        <v>5347</v>
       </c>
       <c r="C451" t="inlineStr">
         <is>
@@ -12214,10 +12160,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
+      <c r="B452" t="n">
+        <v>3443</v>
       </c>
       <c r="C452" t="inlineStr">
         <is>
@@ -12242,10 +12186,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B453" t="n">
+        <v>6274</v>
       </c>
       <c r="C453" t="inlineStr">
         <is>
@@ -12270,10 +12212,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
+      <c r="B454" t="n">
+        <v>2404</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
@@ -12298,10 +12238,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
+      <c r="B455" t="n">
+        <v>8358</v>
       </c>
       <c r="C455" t="inlineStr">
         <is>
@@ -12326,10 +12264,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>4979</t>
-        </is>
+      <c r="B456" t="n">
+        <v>4979</v>
       </c>
       <c r="C456" t="inlineStr">
         <is>
@@ -12354,10 +12290,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
+      <c r="B457" t="n">
+        <v>1326</v>
       </c>
       <c r="C457" t="inlineStr">
         <is>
@@ -12382,10 +12316,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
+      <c r="B458" t="n">
+        <v>6187</v>
       </c>
       <c r="C458" t="inlineStr">
         <is>
@@ -12410,10 +12342,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B459" t="inlineStr">
-        <is>
-          <t>6191</t>
-        </is>
+      <c r="B459" t="n">
+        <v>6191</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
@@ -12438,10 +12368,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>3376</t>
-        </is>
+      <c r="B460" t="n">
+        <v>3376</v>
       </c>
       <c r="C460" t="inlineStr">
         <is>
@@ -12466,10 +12394,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>3264</t>
-        </is>
+      <c r="B461" t="n">
+        <v>3264</v>
       </c>
       <c r="C461" t="inlineStr">
         <is>
@@ -12494,10 +12420,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
+      <c r="B462" t="n">
+        <v>8996</v>
       </c>
       <c r="C462" t="inlineStr">
         <is>
@@ -12522,10 +12446,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
+      <c r="B463" t="n">
+        <v>2408</v>
       </c>
       <c r="C463" t="inlineStr">
         <is>
@@ -12550,10 +12472,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B464" t="inlineStr">
-        <is>
-          <t>3533</t>
-        </is>
+      <c r="B464" t="n">
+        <v>3533</v>
       </c>
       <c r="C464" t="inlineStr">
         <is>
@@ -12578,10 +12498,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B465" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
+      <c r="B465" t="n">
+        <v>6669</v>
       </c>
       <c r="C465" t="inlineStr">
         <is>
@@ -12606,10 +12524,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B466" t="inlineStr">
-        <is>
-          <t>3324</t>
-        </is>
+      <c r="B466" t="n">
+        <v>3324</v>
       </c>
       <c r="C466" t="inlineStr">
         <is>
@@ -12634,10 +12550,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B467" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
+      <c r="B467" t="n">
+        <v>1319</v>
       </c>
       <c r="C467" t="inlineStr">
         <is>
@@ -12662,10 +12576,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B468" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
+      <c r="B468" t="n">
+        <v>2002</v>
       </c>
       <c r="C468" t="inlineStr">
         <is>
@@ -12690,10 +12602,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>3217</t>
-        </is>
+      <c r="B469" t="n">
+        <v>3217</v>
       </c>
       <c r="C469" t="inlineStr">
         <is>
@@ -12718,10 +12628,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B470" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
+      <c r="B470" t="n">
+        <v>3008</v>
       </c>
       <c r="C470" t="inlineStr">
         <is>
@@ -12746,10 +12654,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B471" t="inlineStr">
-        <is>
-          <t>2357</t>
-        </is>
+      <c r="B471" t="n">
+        <v>2357</v>
       </c>
       <c r="C471" t="inlineStr">
         <is>
@@ -12774,10 +12680,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>1815</t>
-        </is>
+      <c r="B472" t="n">
+        <v>1815</v>
       </c>
       <c r="C472" t="inlineStr">
         <is>
@@ -12802,10 +12706,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B473" t="inlineStr">
-        <is>
-          <t>2439</t>
-        </is>
+      <c r="B473" t="n">
+        <v>2439</v>
       </c>
       <c r="C473" t="inlineStr">
         <is>
@@ -12830,10 +12732,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>3045</t>
-        </is>
+      <c r="B474" t="n">
+        <v>3045</v>
       </c>
       <c r="C474" t="inlineStr">
         <is>
@@ -12858,10 +12758,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B475" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
+      <c r="B475" t="n">
+        <v>2313</v>
       </c>
       <c r="C475" t="inlineStr">
         <is>
@@ -12886,10 +12784,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>3583</t>
-        </is>
+      <c r="B476" t="n">
+        <v>3583</v>
       </c>
       <c r="C476" t="inlineStr">
         <is>
@@ -32884,10 +32780,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B178" t="n">
+        <v>2330</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -32916,10 +32810,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B179" t="n">
+        <v>3017</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -32948,10 +32840,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B180" t="n">
+        <v>6223</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -32980,10 +32870,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B181" t="n">
+        <v>6274</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -33012,10 +32900,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
+      <c r="B182" t="n">
+        <v>3665</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -33044,10 +32930,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B183" t="n">
+        <v>2308</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -33076,10 +32960,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B184" t="n">
+        <v>2383</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -33108,10 +32990,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B185" t="n">
+        <v>3653</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -33140,10 +33020,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
+      <c r="B186" t="n">
+        <v>8299</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -33172,10 +33050,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B187" t="n">
+        <v>2345</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -33204,10 +33080,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>3363</t>
-        </is>
+      <c r="B188" t="n">
+        <v>3363</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -33236,10 +33110,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
+      <c r="B189" t="n">
+        <v>3443</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -33268,10 +33140,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>6683</t>
-        </is>
+      <c r="B190" t="n">
+        <v>6683</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -33300,10 +33170,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B191" t="n">
+        <v>6805</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -33332,10 +33200,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B192" t="n">
+        <v>2368</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -33364,10 +33230,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
+      <c r="B193" t="n">
+        <v>8358</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -33396,10 +33260,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B194" t="n">
+        <v>3037</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -33428,10 +33290,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
+      <c r="B195" t="n">
+        <v>2337</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -33460,10 +33320,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="B196" t="n">
+        <v>2360</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -33492,10 +33350,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>2455</t>
-        </is>
+      <c r="B197" t="n">
+        <v>2455</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -33524,10 +33380,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
+      <c r="B198" t="n">
+        <v>6510</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -33556,10 +33410,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>6442</t>
-        </is>
+      <c r="B199" t="n">
+        <v>6442</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -33588,10 +33440,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
+      <c r="B200" t="n">
+        <v>7769</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -33620,10 +33470,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>6739</t>
-        </is>
+      <c r="B201" t="n">
+        <v>6739</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -33652,10 +33500,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
+      <c r="B202" t="n">
+        <v>6770</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -41234,10 +41080,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
+      <c r="B270" t="n">
+        <v>2059</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -41249,10 +41093,8 @@
           <t>7,000</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
+      <c r="E270" t="n">
+        <v>1.65</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -41266,10 +41108,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B271" t="n">
+        <v>2308</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -41281,10 +41121,8 @@
           <t>29,499</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>2.91</t>
-        </is>
+      <c r="E271" t="n">
+        <v>2.91</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -41298,10 +41136,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
+      <c r="B272" t="n">
+        <v>2313</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -41313,10 +41149,8 @@
           <t>110,000</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
+      <c r="E272" t="n">
+        <v>1.94</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -41330,10 +41164,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B273" t="n">
+        <v>2330</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -41345,10 +41177,8 @@
           <t>136,999</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>16.25</t>
-        </is>
+      <c r="E273" t="n">
+        <v>16.25</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -41362,10 +41192,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B274" t="n">
+        <v>2345</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -41377,10 +41205,8 @@
           <t>56,000</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>6.05</t>
-        </is>
+      <c r="E274" t="n">
+        <v>6.05</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -41394,10 +41220,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="B275" t="n">
+        <v>2360</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -41409,10 +41233,8 @@
           <t>41,000</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>4.32</t>
-        </is>
+      <c r="E275" t="n">
+        <v>4.32</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -41426,10 +41248,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B276" t="n">
+        <v>2368</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -41441,10 +41261,8 @@
           <t>60,000</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>3.62</t>
-        </is>
+      <c r="E276" t="n">
+        <v>3.62</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -41458,10 +41276,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B277" t="n">
+        <v>2383</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -41473,10 +41289,8 @@
           <t>32,000</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>6.08</t>
-        </is>
+      <c r="E277" t="n">
+        <v>6.08</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -41490,10 +41304,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
+      <c r="B278" t="n">
+        <v>2449</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -41505,10 +41317,8 @@
           <t>122,000</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
+      <c r="E278" t="n">
+        <v>2.22</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -41522,10 +41332,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>2467</t>
-        </is>
+      <c r="B279" t="n">
+        <v>2467</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -41537,10 +41345,8 @@
           <t>59,000</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
+      <c r="E279" t="n">
+        <v>1.6</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -41554,10 +41360,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B280" t="n">
+        <v>3017</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -41569,10 +41373,8 @@
           <t>41,500</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>5.95</t>
-        </is>
+      <c r="E280" t="n">
+        <v>5.95</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -41586,10 +41388,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B281" t="n">
+        <v>3037</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -41601,10 +41401,8 @@
           <t>122,001</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>4.02</t>
-        </is>
+      <c r="E281" t="n">
+        <v>4.02</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -41618,10 +41416,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>3105</t>
-        </is>
+      <c r="B282" t="n">
+        <v>3105</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -41633,10 +41429,8 @@
           <t>44,000</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
+      <c r="E282" t="n">
+        <v>1.1</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -41650,10 +41444,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>3260</t>
-        </is>
+      <c r="B283" t="n">
+        <v>3260</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -41665,10 +41457,8 @@
           <t>14,000</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
+      <c r="E283" t="n">
+        <v>0.36</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -41682,10 +41472,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>3324</t>
-        </is>
+      <c r="B284" t="n">
+        <v>3324</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -41697,10 +41485,8 @@
           <t>3,000</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
+      <c r="E284" t="n">
+        <v>0.19</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -41714,10 +41500,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
+      <c r="B285" t="n">
+        <v>3443</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -41729,10 +41513,8 @@
           <t>50</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
+      <c r="E285" t="n">
+        <v>0.01</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -41746,10 +41528,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B286" t="n">
+        <v>3653</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -41761,10 +41541,8 @@
           <t>18,000</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="E286" t="n">
+        <v>4.75</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -41778,10 +41556,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
+      <c r="B287" t="n">
+        <v>3661</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -41793,10 +41569,8 @@
           <t>7,500</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
+      <c r="E287" t="n">
+        <v>1.49</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -41810,10 +41584,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
+      <c r="B288" t="n">
+        <v>3665</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -41825,10 +41597,8 @@
           <t>26,000</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>3.16</t>
-        </is>
+      <c r="E288" t="n">
+        <v>3.16</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -41842,10 +41612,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
+      <c r="B289" t="n">
+        <v>3711</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -41857,10 +41625,8 @@
           <t>51,000</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
+      <c r="E289" t="n">
+        <v>1.18</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -41874,10 +41640,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>4904</t>
-        </is>
+      <c r="B290" t="n">
+        <v>4904</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -41889,10 +41653,8 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="E290" t="n">
+        <v>0</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -41906,10 +41668,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>4979</t>
-        </is>
+      <c r="B291" t="n">
+        <v>4979</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -41921,10 +41681,8 @@
           <t>36,000</t>
         </is>
       </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
+      <c r="E291" t="n">
+        <v>0.93</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -41938,10 +41696,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
+      <c r="B292" t="n">
+        <v>5274</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -41953,10 +41709,8 @@
           <t>4,600</t>
         </is>
       </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
+      <c r="E292" t="n">
+        <v>3.47</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -41970,10 +41724,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>5536</t>
-        </is>
+      <c r="B293" t="n">
+        <v>5536</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -41985,10 +41737,8 @@
           <t>27,000</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
+      <c r="E293" t="n">
+        <v>1.33</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -42002,10 +41752,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B294" t="n">
+        <v>6223</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -42017,10 +41765,8 @@
           <t>22,000</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>5.26</t>
-        </is>
+      <c r="E294" t="n">
+        <v>5.26</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -42034,10 +41780,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>6257</t>
-        </is>
+      <c r="B295" t="n">
+        <v>6257</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -42049,10 +41793,8 @@
           <t>80,000</t>
         </is>
       </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
+      <c r="E295" t="n">
+        <v>0.76</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -42066,10 +41808,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B296" t="n">
+        <v>6274</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -42081,10 +41821,8 @@
           <t>80,000</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>3.27</t>
-        </is>
+      <c r="E296" t="n">
+        <v>3.27</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -42098,10 +41836,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>6442</t>
-        </is>
+      <c r="B297" t="n">
+        <v>6442</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -42113,10 +41849,8 @@
           <t>12,000</t>
         </is>
       </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
+      <c r="E297" t="n">
+        <v>1.66</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -42130,10 +41864,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
+      <c r="B298" t="n">
+        <v>6510</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -42145,10 +41877,8 @@
           <t>8,000</t>
         </is>
       </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
+      <c r="E298" t="n">
+        <v>1.69</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -42162,10 +41892,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
+      <c r="B299" t="n">
+        <v>6515</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -42177,10 +41905,8 @@
           <t>9,100</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>4.70</t>
-        </is>
+      <c r="E299" t="n">
+        <v>4.7</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -42194,10 +41920,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B300" t="n">
+        <v>6805</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -42209,10 +41933,8 @@
           <t>29,001</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>3.61</t>
-        </is>
+      <c r="E300" t="n">
+        <v>3.61</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -42226,10 +41948,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
+      <c r="B301" t="n">
+        <v>8046</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -42241,10 +41961,8 @@
           <t>66,000</t>
         </is>
       </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>2.42</t>
-        </is>
+      <c r="E301" t="n">
+        <v>2.42</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -53302,10 +53020,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B425" t="n">
+        <v>2330</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
@@ -53330,10 +53046,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B426" t="n">
+        <v>2383</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
@@ -53358,10 +53072,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B427" t="n">
+        <v>2308</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
@@ -53386,10 +53098,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B428" t="n">
+        <v>3017</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
@@ -53414,10 +53124,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B429" t="n">
+        <v>3653</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
@@ -53442,10 +53150,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B430" t="n">
+        <v>2345</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
@@ -53470,10 +53176,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B431" t="n">
+        <v>2368</v>
       </c>
       <c r="C431" t="inlineStr">
         <is>
@@ -53498,10 +53202,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
+      <c r="B432" t="n">
+        <v>3665</v>
       </c>
       <c r="C432" t="inlineStr">
         <is>
@@ -53526,10 +53228,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B433" t="n">
+        <v>6223</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
@@ -53554,10 +53254,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B434" t="n">
+        <v>3037</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
@@ -53582,10 +53280,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
+      <c r="B435" t="n">
+        <v>8046</v>
       </c>
       <c r="C435" t="inlineStr">
         <is>
@@ -53610,10 +53306,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
+      <c r="B436" t="n">
+        <v>5274</v>
       </c>
       <c r="C436" t="inlineStr">
         <is>
@@ -53638,10 +53332,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
+      <c r="B437" t="n">
+        <v>2327</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
@@ -53666,10 +53358,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
+      <c r="B438" t="n">
+        <v>3711</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
@@ -53694,10 +53384,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
+      <c r="B439" t="n">
+        <v>6515</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
@@ -53722,10 +53410,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
+      <c r="B440" t="n">
+        <v>2449</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
@@ -53750,10 +53436,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
+      <c r="B441" t="n">
+        <v>6510</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
@@ -53778,10 +53462,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>3211</t>
-        </is>
+      <c r="B442" t="n">
+        <v>3211</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
@@ -53806,10 +53488,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>8210</t>
-        </is>
+      <c r="B443" t="n">
+        <v>8210</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
@@ -53834,10 +53514,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B444" t="n">
+        <v>6805</v>
       </c>
       <c r="C444" t="inlineStr">
         <is>
@@ -53862,10 +53540,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
+      <c r="B445" t="n">
+        <v>1303</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
@@ -53890,10 +53566,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
+      <c r="B446" t="n">
+        <v>3661</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
@@ -53918,10 +53592,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
+      <c r="B447" t="n">
+        <v>3189</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
@@ -53946,10 +53618,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>6139</t>
-        </is>
+      <c r="B448" t="n">
+        <v>6139</v>
       </c>
       <c r="C448" t="inlineStr">
         <is>
@@ -53974,10 +53644,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
+      <c r="B449" t="n">
+        <v>2454</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
@@ -54002,10 +53670,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>6488</t>
-        </is>
+      <c r="B450" t="n">
+        <v>6488</v>
       </c>
       <c r="C450" t="inlineStr">
         <is>
@@ -54030,10 +53696,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>5347</t>
-        </is>
+      <c r="B451" t="n">
+        <v>5347</v>
       </c>
       <c r="C451" t="inlineStr">
         <is>
@@ -54058,10 +53722,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
+      <c r="B452" t="n">
+        <v>3443</v>
       </c>
       <c r="C452" t="inlineStr">
         <is>
@@ -54086,10 +53748,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B453" t="n">
+        <v>6274</v>
       </c>
       <c r="C453" t="inlineStr">
         <is>
@@ -54114,10 +53774,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
+      <c r="B454" t="n">
+        <v>2404</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
@@ -54142,10 +53800,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
+      <c r="B455" t="n">
+        <v>8358</v>
       </c>
       <c r="C455" t="inlineStr">
         <is>
@@ -54170,10 +53826,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>4979</t>
-        </is>
+      <c r="B456" t="n">
+        <v>4979</v>
       </c>
       <c r="C456" t="inlineStr">
         <is>
@@ -54198,10 +53852,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
+      <c r="B457" t="n">
+        <v>1326</v>
       </c>
       <c r="C457" t="inlineStr">
         <is>
@@ -54226,10 +53878,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
+      <c r="B458" t="n">
+        <v>6187</v>
       </c>
       <c r="C458" t="inlineStr">
         <is>
@@ -54254,10 +53904,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B459" t="inlineStr">
-        <is>
-          <t>6191</t>
-        </is>
+      <c r="B459" t="n">
+        <v>6191</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
@@ -54282,10 +53930,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>3376</t>
-        </is>
+      <c r="B460" t="n">
+        <v>3376</v>
       </c>
       <c r="C460" t="inlineStr">
         <is>
@@ -54310,10 +53956,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>3264</t>
-        </is>
+      <c r="B461" t="n">
+        <v>3264</v>
       </c>
       <c r="C461" t="inlineStr">
         <is>
@@ -54338,10 +53982,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
+      <c r="B462" t="n">
+        <v>8996</v>
       </c>
       <c r="C462" t="inlineStr">
         <is>
@@ -54366,10 +54008,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
+      <c r="B463" t="n">
+        <v>2408</v>
       </c>
       <c r="C463" t="inlineStr">
         <is>
@@ -54394,10 +54034,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B464" t="inlineStr">
-        <is>
-          <t>3533</t>
-        </is>
+      <c r="B464" t="n">
+        <v>3533</v>
       </c>
       <c r="C464" t="inlineStr">
         <is>
@@ -54422,10 +54060,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B465" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
+      <c r="B465" t="n">
+        <v>6669</v>
       </c>
       <c r="C465" t="inlineStr">
         <is>
@@ -54450,10 +54086,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B466" t="inlineStr">
-        <is>
-          <t>3324</t>
-        </is>
+      <c r="B466" t="n">
+        <v>3324</v>
       </c>
       <c r="C466" t="inlineStr">
         <is>
@@ -54478,10 +54112,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B467" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
+      <c r="B467" t="n">
+        <v>1319</v>
       </c>
       <c r="C467" t="inlineStr">
         <is>
@@ -54506,10 +54138,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B468" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
+      <c r="B468" t="n">
+        <v>2002</v>
       </c>
       <c r="C468" t="inlineStr">
         <is>
@@ -54534,10 +54164,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>3217</t>
-        </is>
+      <c r="B469" t="n">
+        <v>3217</v>
       </c>
       <c r="C469" t="inlineStr">
         <is>
@@ -54562,10 +54190,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B470" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
+      <c r="B470" t="n">
+        <v>3008</v>
       </c>
       <c r="C470" t="inlineStr">
         <is>
@@ -54590,10 +54216,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B471" t="inlineStr">
-        <is>
-          <t>2357</t>
-        </is>
+      <c r="B471" t="n">
+        <v>2357</v>
       </c>
       <c r="C471" t="inlineStr">
         <is>
@@ -54618,10 +54242,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>1815</t>
-        </is>
+      <c r="B472" t="n">
+        <v>1815</v>
       </c>
       <c r="C472" t="inlineStr">
         <is>
@@ -54646,10 +54268,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B473" t="inlineStr">
-        <is>
-          <t>2439</t>
-        </is>
+      <c r="B473" t="n">
+        <v>2439</v>
       </c>
       <c r="C473" t="inlineStr">
         <is>
@@ -54674,10 +54294,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>3045</t>
-        </is>
+      <c r="B474" t="n">
+        <v>3045</v>
       </c>
       <c r="C474" t="inlineStr">
         <is>
@@ -54702,10 +54320,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B475" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
+      <c r="B475" t="n">
+        <v>2313</v>
       </c>
       <c r="C475" t="inlineStr">
         <is>
@@ -54730,10 +54346,8 @@
           <t>00981A</t>
         </is>
       </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>3583</t>
-        </is>
+      <c r="B476" t="n">
+        <v>3583</v>
       </c>
       <c r="C476" t="inlineStr">
         <is>
@@ -74544,10 +74158,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1117" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B1117" t="n">
+        <v>2330</v>
       </c>
       <c r="C1117" t="inlineStr">
         <is>
@@ -74576,10 +74188,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1118" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B1118" t="n">
+        <v>3017</v>
       </c>
       <c r="C1118" t="inlineStr">
         <is>
@@ -74608,10 +74218,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1119" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B1119" t="n">
+        <v>6223</v>
       </c>
       <c r="C1119" t="inlineStr">
         <is>
@@ -74640,10 +74248,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1120" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B1120" t="n">
+        <v>6274</v>
       </c>
       <c r="C1120" t="inlineStr">
         <is>
@@ -74672,10 +74278,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1121" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
+      <c r="B1121" t="n">
+        <v>3665</v>
       </c>
       <c r="C1121" t="inlineStr">
         <is>
@@ -74704,10 +74308,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1122" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B1122" t="n">
+        <v>2308</v>
       </c>
       <c r="C1122" t="inlineStr">
         <is>
@@ -74736,10 +74338,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1123" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B1123" t="n">
+        <v>2383</v>
       </c>
       <c r="C1123" t="inlineStr">
         <is>
@@ -74768,10 +74368,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1124" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B1124" t="n">
+        <v>3653</v>
       </c>
       <c r="C1124" t="inlineStr">
         <is>
@@ -74800,10 +74398,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1125" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
+      <c r="B1125" t="n">
+        <v>8299</v>
       </c>
       <c r="C1125" t="inlineStr">
         <is>
@@ -74832,10 +74428,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1126" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B1126" t="n">
+        <v>2345</v>
       </c>
       <c r="C1126" t="inlineStr">
         <is>
@@ -74864,10 +74458,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1127" t="inlineStr">
-        <is>
-          <t>3363</t>
-        </is>
+      <c r="B1127" t="n">
+        <v>3363</v>
       </c>
       <c r="C1127" t="inlineStr">
         <is>
@@ -74896,10 +74488,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1128" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
+      <c r="B1128" t="n">
+        <v>3443</v>
       </c>
       <c r="C1128" t="inlineStr">
         <is>
@@ -74928,10 +74518,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1129" t="inlineStr">
-        <is>
-          <t>6683</t>
-        </is>
+      <c r="B1129" t="n">
+        <v>6683</v>
       </c>
       <c r="C1129" t="inlineStr">
         <is>
@@ -74960,10 +74548,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1130" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B1130" t="n">
+        <v>6805</v>
       </c>
       <c r="C1130" t="inlineStr">
         <is>
@@ -74992,10 +74578,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1131" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B1131" t="n">
+        <v>2368</v>
       </c>
       <c r="C1131" t="inlineStr">
         <is>
@@ -75024,10 +74608,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1132" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
+      <c r="B1132" t="n">
+        <v>8358</v>
       </c>
       <c r="C1132" t="inlineStr">
         <is>
@@ -75056,10 +74638,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1133" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B1133" t="n">
+        <v>3037</v>
       </c>
       <c r="C1133" t="inlineStr">
         <is>
@@ -75088,10 +74668,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1134" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
+      <c r="B1134" t="n">
+        <v>2337</v>
       </c>
       <c r="C1134" t="inlineStr">
         <is>
@@ -75120,10 +74698,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1135" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="B1135" t="n">
+        <v>2360</v>
       </c>
       <c r="C1135" t="inlineStr">
         <is>
@@ -75152,10 +74728,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1136" t="inlineStr">
-        <is>
-          <t>2455</t>
-        </is>
+      <c r="B1136" t="n">
+        <v>2455</v>
       </c>
       <c r="C1136" t="inlineStr">
         <is>
@@ -75184,10 +74758,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1137" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
+      <c r="B1137" t="n">
+        <v>6510</v>
       </c>
       <c r="C1137" t="inlineStr">
         <is>
@@ -75216,10 +74788,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1138" t="inlineStr">
-        <is>
-          <t>6442</t>
-        </is>
+      <c r="B1138" t="n">
+        <v>6442</v>
       </c>
       <c r="C1138" t="inlineStr">
         <is>
@@ -75248,10 +74818,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1139" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
+      <c r="B1139" t="n">
+        <v>7769</v>
       </c>
       <c r="C1139" t="inlineStr">
         <is>
@@ -75280,10 +74848,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1140" t="inlineStr">
-        <is>
-          <t>6739</t>
-        </is>
+      <c r="B1140" t="n">
+        <v>6739</v>
       </c>
       <c r="C1140" t="inlineStr">
         <is>
@@ -75312,10 +74878,8 @@
           <t>00987A</t>
         </is>
       </c>
-      <c r="B1141" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
+      <c r="B1141" t="n">
+        <v>6770</v>
       </c>
       <c r="C1141" t="inlineStr">
         <is>
@@ -82848,10 +82412,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1410" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
+      <c r="B1410" t="n">
+        <v>2059</v>
       </c>
       <c r="C1410" t="inlineStr">
         <is>
@@ -82863,10 +82425,8 @@
           <t>7,000</t>
         </is>
       </c>
-      <c r="E1410" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
+      <c r="E1410" t="n">
+        <v>1.65</v>
       </c>
       <c r="F1410" t="inlineStr">
         <is>
@@ -82880,10 +82440,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1411" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
+      <c r="B1411" t="n">
+        <v>2308</v>
       </c>
       <c r="C1411" t="inlineStr">
         <is>
@@ -82895,10 +82453,8 @@
           <t>29,499</t>
         </is>
       </c>
-      <c r="E1411" t="inlineStr">
-        <is>
-          <t>2.91</t>
-        </is>
+      <c r="E1411" t="n">
+        <v>2.91</v>
       </c>
       <c r="F1411" t="inlineStr">
         <is>
@@ -82912,10 +82468,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1412" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
+      <c r="B1412" t="n">
+        <v>2313</v>
       </c>
       <c r="C1412" t="inlineStr">
         <is>
@@ -82927,10 +82481,8 @@
           <t>110,000</t>
         </is>
       </c>
-      <c r="E1412" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
+      <c r="E1412" t="n">
+        <v>1.94</v>
       </c>
       <c r="F1412" t="inlineStr">
         <is>
@@ -82944,10 +82496,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1413" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="B1413" t="n">
+        <v>2330</v>
       </c>
       <c r="C1413" t="inlineStr">
         <is>
@@ -82959,10 +82509,8 @@
           <t>136,999</t>
         </is>
       </c>
-      <c r="E1413" t="inlineStr">
-        <is>
-          <t>16.25</t>
-        </is>
+      <c r="E1413" t="n">
+        <v>16.25</v>
       </c>
       <c r="F1413" t="inlineStr">
         <is>
@@ -82976,10 +82524,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1414" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
+      <c r="B1414" t="n">
+        <v>2345</v>
       </c>
       <c r="C1414" t="inlineStr">
         <is>
@@ -82991,10 +82537,8 @@
           <t>56,000</t>
         </is>
       </c>
-      <c r="E1414" t="inlineStr">
-        <is>
-          <t>6.05</t>
-        </is>
+      <c r="E1414" t="n">
+        <v>6.05</v>
       </c>
       <c r="F1414" t="inlineStr">
         <is>
@@ -83008,10 +82552,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1415" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="B1415" t="n">
+        <v>2360</v>
       </c>
       <c r="C1415" t="inlineStr">
         <is>
@@ -83023,10 +82565,8 @@
           <t>41,000</t>
         </is>
       </c>
-      <c r="E1415" t="inlineStr">
-        <is>
-          <t>4.32</t>
-        </is>
+      <c r="E1415" t="n">
+        <v>4.32</v>
       </c>
       <c r="F1415" t="inlineStr">
         <is>
@@ -83040,10 +82580,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1416" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
+      <c r="B1416" t="n">
+        <v>2368</v>
       </c>
       <c r="C1416" t="inlineStr">
         <is>
@@ -83055,10 +82593,8 @@
           <t>60,000</t>
         </is>
       </c>
-      <c r="E1416" t="inlineStr">
-        <is>
-          <t>3.62</t>
-        </is>
+      <c r="E1416" t="n">
+        <v>3.62</v>
       </c>
       <c r="F1416" t="inlineStr">
         <is>
@@ -83072,10 +82608,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1417" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="B1417" t="n">
+        <v>2383</v>
       </c>
       <c r="C1417" t="inlineStr">
         <is>
@@ -83087,10 +82621,8 @@
           <t>32,000</t>
         </is>
       </c>
-      <c r="E1417" t="inlineStr">
-        <is>
-          <t>6.08</t>
-        </is>
+      <c r="E1417" t="n">
+        <v>6.08</v>
       </c>
       <c r="F1417" t="inlineStr">
         <is>
@@ -83104,10 +82636,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1418" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
+      <c r="B1418" t="n">
+        <v>2449</v>
       </c>
       <c r="C1418" t="inlineStr">
         <is>
@@ -83119,10 +82649,8 @@
           <t>122,000</t>
         </is>
       </c>
-      <c r="E1418" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
+      <c r="E1418" t="n">
+        <v>2.22</v>
       </c>
       <c r="F1418" t="inlineStr">
         <is>
@@ -83136,10 +82664,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1419" t="inlineStr">
-        <is>
-          <t>2467</t>
-        </is>
+      <c r="B1419" t="n">
+        <v>2467</v>
       </c>
       <c r="C1419" t="inlineStr">
         <is>
@@ -83151,10 +82677,8 @@
           <t>59,000</t>
         </is>
       </c>
-      <c r="E1419" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
+      <c r="E1419" t="n">
+        <v>1.6</v>
       </c>
       <c r="F1419" t="inlineStr">
         <is>
@@ -83168,10 +82692,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1420" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
+      <c r="B1420" t="n">
+        <v>3017</v>
       </c>
       <c r="C1420" t="inlineStr">
         <is>
@@ -83183,10 +82705,8 @@
           <t>41,500</t>
         </is>
       </c>
-      <c r="E1420" t="inlineStr">
-        <is>
-          <t>5.95</t>
-        </is>
+      <c r="E1420" t="n">
+        <v>5.95</v>
       </c>
       <c r="F1420" t="inlineStr">
         <is>
@@ -83200,10 +82720,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1421" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
+      <c r="B1421" t="n">
+        <v>3037</v>
       </c>
       <c r="C1421" t="inlineStr">
         <is>
@@ -83215,10 +82733,8 @@
           <t>122,001</t>
         </is>
       </c>
-      <c r="E1421" t="inlineStr">
-        <is>
-          <t>4.02</t>
-        </is>
+      <c r="E1421" t="n">
+        <v>4.02</v>
       </c>
       <c r="F1421" t="inlineStr">
         <is>
@@ -83232,10 +82748,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1422" t="inlineStr">
-        <is>
-          <t>3105</t>
-        </is>
+      <c r="B1422" t="n">
+        <v>3105</v>
       </c>
       <c r="C1422" t="inlineStr">
         <is>
@@ -83247,10 +82761,8 @@
           <t>44,000</t>
         </is>
       </c>
-      <c r="E1422" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
+      <c r="E1422" t="n">
+        <v>1.1</v>
       </c>
       <c r="F1422" t="inlineStr">
         <is>
@@ -83264,10 +82776,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1423" t="inlineStr">
-        <is>
-          <t>3260</t>
-        </is>
+      <c r="B1423" t="n">
+        <v>3260</v>
       </c>
       <c r="C1423" t="inlineStr">
         <is>
@@ -83279,10 +82789,8 @@
           <t>14,000</t>
         </is>
       </c>
-      <c r="E1423" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
+      <c r="E1423" t="n">
+        <v>0.36</v>
       </c>
       <c r="F1423" t="inlineStr">
         <is>
@@ -83296,10 +82804,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1424" t="inlineStr">
-        <is>
-          <t>3324</t>
-        </is>
+      <c r="B1424" t="n">
+        <v>3324</v>
       </c>
       <c r="C1424" t="inlineStr">
         <is>
@@ -83311,10 +82817,8 @@
           <t>3,000</t>
         </is>
       </c>
-      <c r="E1424" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
+      <c r="E1424" t="n">
+        <v>0.19</v>
       </c>
       <c r="F1424" t="inlineStr">
         <is>
@@ -83328,10 +82832,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1425" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
+      <c r="B1425" t="n">
+        <v>3443</v>
       </c>
       <c r="C1425" t="inlineStr">
         <is>
@@ -83343,10 +82845,8 @@
           <t>50</t>
         </is>
       </c>
-      <c r="E1425" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
+      <c r="E1425" t="n">
+        <v>0.01</v>
       </c>
       <c r="F1425" t="inlineStr">
         <is>
@@ -83360,10 +82860,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1426" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
+      <c r="B1426" t="n">
+        <v>3653</v>
       </c>
       <c r="C1426" t="inlineStr">
         <is>
@@ -83375,10 +82873,8 @@
           <t>18,000</t>
         </is>
       </c>
-      <c r="E1426" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="E1426" t="n">
+        <v>4.75</v>
       </c>
       <c r="F1426" t="inlineStr">
         <is>
@@ -83392,10 +82888,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1427" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
+      <c r="B1427" t="n">
+        <v>3661</v>
       </c>
       <c r="C1427" t="inlineStr">
         <is>
@@ -83407,10 +82901,8 @@
           <t>7,500</t>
         </is>
       </c>
-      <c r="E1427" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
+      <c r="E1427" t="n">
+        <v>1.49</v>
       </c>
       <c r="F1427" t="inlineStr">
         <is>
@@ -83424,10 +82916,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1428" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
+      <c r="B1428" t="n">
+        <v>3665</v>
       </c>
       <c r="C1428" t="inlineStr">
         <is>
@@ -83439,10 +82929,8 @@
           <t>26,000</t>
         </is>
       </c>
-      <c r="E1428" t="inlineStr">
-        <is>
-          <t>3.16</t>
-        </is>
+      <c r="E1428" t="n">
+        <v>3.16</v>
       </c>
       <c r="F1428" t="inlineStr">
         <is>
@@ -83456,10 +82944,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1429" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
+      <c r="B1429" t="n">
+        <v>3711</v>
       </c>
       <c r="C1429" t="inlineStr">
         <is>
@@ -83471,10 +82957,8 @@
           <t>51,000</t>
         </is>
       </c>
-      <c r="E1429" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
+      <c r="E1429" t="n">
+        <v>1.18</v>
       </c>
       <c r="F1429" t="inlineStr">
         <is>
@@ -83488,10 +82972,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1430" t="inlineStr">
-        <is>
-          <t>4904</t>
-        </is>
+      <c r="B1430" t="n">
+        <v>4904</v>
       </c>
       <c r="C1430" t="inlineStr">
         <is>
@@ -83503,10 +82985,8 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E1430" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="E1430" t="n">
+        <v>0</v>
       </c>
       <c r="F1430" t="inlineStr">
         <is>
@@ -83520,10 +83000,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1431" t="inlineStr">
-        <is>
-          <t>4979</t>
-        </is>
+      <c r="B1431" t="n">
+        <v>4979</v>
       </c>
       <c r="C1431" t="inlineStr">
         <is>
@@ -83535,10 +83013,8 @@
           <t>36,000</t>
         </is>
       </c>
-      <c r="E1431" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
+      <c r="E1431" t="n">
+        <v>0.93</v>
       </c>
       <c r="F1431" t="inlineStr">
         <is>
@@ -83552,10 +83028,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1432" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
+      <c r="B1432" t="n">
+        <v>5274</v>
       </c>
       <c r="C1432" t="inlineStr">
         <is>
@@ -83567,10 +83041,8 @@
           <t>4,600</t>
         </is>
       </c>
-      <c r="E1432" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
+      <c r="E1432" t="n">
+        <v>3.47</v>
       </c>
       <c r="F1432" t="inlineStr">
         <is>
@@ -83584,10 +83056,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1433" t="inlineStr">
-        <is>
-          <t>5536</t>
-        </is>
+      <c r="B1433" t="n">
+        <v>5536</v>
       </c>
       <c r="C1433" t="inlineStr">
         <is>
@@ -83599,10 +83069,8 @@
           <t>27,000</t>
         </is>
       </c>
-      <c r="E1433" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
+      <c r="E1433" t="n">
+        <v>1.33</v>
       </c>
       <c r="F1433" t="inlineStr">
         <is>
@@ -83616,10 +83084,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1434" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
+      <c r="B1434" t="n">
+        <v>6223</v>
       </c>
       <c r="C1434" t="inlineStr">
         <is>
@@ -83631,10 +83097,8 @@
           <t>22,000</t>
         </is>
       </c>
-      <c r="E1434" t="inlineStr">
-        <is>
-          <t>5.26</t>
-        </is>
+      <c r="E1434" t="n">
+        <v>5.26</v>
       </c>
       <c r="F1434" t="inlineStr">
         <is>
@@ -83648,10 +83112,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1435" t="inlineStr">
-        <is>
-          <t>6257</t>
-        </is>
+      <c r="B1435" t="n">
+        <v>6257</v>
       </c>
       <c r="C1435" t="inlineStr">
         <is>
@@ -83663,10 +83125,8 @@
           <t>80,000</t>
         </is>
       </c>
-      <c r="E1435" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
+      <c r="E1435" t="n">
+        <v>0.76</v>
       </c>
       <c r="F1435" t="inlineStr">
         <is>
@@ -83680,10 +83140,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1436" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
+      <c r="B1436" t="n">
+        <v>6274</v>
       </c>
       <c r="C1436" t="inlineStr">
         <is>
@@ -83695,10 +83153,8 @@
           <t>80,000</t>
         </is>
       </c>
-      <c r="E1436" t="inlineStr">
-        <is>
-          <t>3.27</t>
-        </is>
+      <c r="E1436" t="n">
+        <v>3.27</v>
       </c>
       <c r="F1436" t="inlineStr">
         <is>
@@ -83712,10 +83168,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1437" t="inlineStr">
-        <is>
-          <t>6442</t>
-        </is>
+      <c r="B1437" t="n">
+        <v>6442</v>
       </c>
       <c r="C1437" t="inlineStr">
         <is>
@@ -83727,10 +83181,8 @@
           <t>12,000</t>
         </is>
       </c>
-      <c r="E1437" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
+      <c r="E1437" t="n">
+        <v>1.66</v>
       </c>
       <c r="F1437" t="inlineStr">
         <is>
@@ -83744,10 +83196,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1438" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
+      <c r="B1438" t="n">
+        <v>6510</v>
       </c>
       <c r="C1438" t="inlineStr">
         <is>
@@ -83759,10 +83209,8 @@
           <t>8,000</t>
         </is>
       </c>
-      <c r="E1438" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
+      <c r="E1438" t="n">
+        <v>1.69</v>
       </c>
       <c r="F1438" t="inlineStr">
         <is>
@@ -83776,10 +83224,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1439" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
+      <c r="B1439" t="n">
+        <v>6515</v>
       </c>
       <c r="C1439" t="inlineStr">
         <is>
@@ -83791,10 +83237,8 @@
           <t>9,100</t>
         </is>
       </c>
-      <c r="E1439" t="inlineStr">
-        <is>
-          <t>4.70</t>
-        </is>
+      <c r="E1439" t="n">
+        <v>4.7</v>
       </c>
       <c r="F1439" t="inlineStr">
         <is>
@@ -83808,10 +83252,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1440" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
+      <c r="B1440" t="n">
+        <v>6805</v>
       </c>
       <c r="C1440" t="inlineStr">
         <is>
@@ -83823,10 +83265,8 @@
           <t>29,001</t>
         </is>
       </c>
-      <c r="E1440" t="inlineStr">
-        <is>
-          <t>3.61</t>
-        </is>
+      <c r="E1440" t="n">
+        <v>3.61</v>
       </c>
       <c r="F1440" t="inlineStr">
         <is>
@@ -83840,10 +83280,8 @@
           <t>00994A</t>
         </is>
       </c>
-      <c r="B1441" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
+      <c r="B1441" t="n">
+        <v>8046</v>
       </c>
       <c r="C1441" t="inlineStr">
         <is>
@@ -83855,10 +83293,8 @@
           <t>66,000</t>
         </is>
       </c>
-      <c r="E1441" t="inlineStr">
-        <is>
-          <t>2.42</t>
-        </is>
+      <c r="E1441" t="n">
+        <v>2.42</v>
       </c>
       <c r="F1441" t="inlineStr">
         <is>
